--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 04-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 04-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 05-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 05-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -161,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +177,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -306,12 +307,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$8</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$8</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -341,12 +342,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$8</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$8</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -453,12 +454,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$8</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$8</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -863,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -883,7 +884,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 04/08/2026 (3j). Livree. lun-sam. Mise a jour 04/08/2026.</t>
+          <t>01/07 au 06/08/2026 (5j). Livree. lun-sam. Mise a jour 06/08/2026.</t>
         </is>
       </c>
     </row>
@@ -926,14 +927,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>141.2</v>
+        <v>209.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>47.1</v>
+        <v>41.8</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-26.4 t/j</t>
+          <t>-31.7 t/j</t>
         </is>
       </c>
     </row>
@@ -949,14 +950,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>64.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>21.6</v>
+        <v>18.9</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-10.1 t/j</t>
+          <t>-12.8 t/j</t>
         </is>
       </c>
     </row>
@@ -972,21 +973,21 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>46.6</v>
+        <v>61.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15.5</v>
+        <v>12.3</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-42.4 t/j</t>
+          <t>-45.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -995,21 +996,21 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>31.4</v>
+        <v>49.3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-0.8 t/j</t>
+          <t>-12.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1018,67 +1019,67 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>27.9</v>
+        <v>39.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-4.5 t/j</t>
+          <t>-3.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>24.7</v>
+        <v>35.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-14.3 t/j</t>
+          <t>-9.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>24.6</v>
+        <v>34.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-8.1 t/j</t>
+          <t>-5.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1087,67 +1088,67 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20.6</v>
+        <v>33.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-2.3 t/j</t>
+          <t>-7.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>17.2</v>
+        <v>23.9</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-0.1 t/j</t>
+        <v>4.8</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-1.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>16.3</v>
+        <v>23.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.5 t/j</t>
+          <t>-4.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1156,178 +1157,201 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>15.3</v>
+        <v>22.9</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-7.0 t/j</t>
+          <t>-1.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>13.9</v>
+        <v>20.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-1.7 t/j</t>
+          <t>-1.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.6</v>
+        <v>11.3</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>+0.4 t/j</t>
+        <v>2.3</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-8.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>7.8</v>
+        <v>11.1</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-8.4 t/j</t>
+          <t>-0.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL Ouest</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E19" s="7" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>AGENCE MAROUA</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>nouveau</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>TOTAL Centre</t>
+          <t>TOTAL Ouest</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>131.3</v>
+        <v>339.5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>43.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t>TOTAL Centre</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>TOTAL Littoral</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>154.1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n">
-        <v>461.9</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>154</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>-126.3 t/j vs 280.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n">
+        <v>675.4</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>-145.1 t/j vs 280.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Moyenne/jour globale: 154.0 t/j (3079 sacs) sur 3j.</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne/jour globale: 135.1 t/j (2701 sacs) sur 5j.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 280.2 t/j (5604 sacs) sur 27j.</t>
         </is>
@@ -1344,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1359,14 +1383,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 04/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 05/08/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 04/08/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 06/08/2026.</t>
         </is>
       </c>
     </row>
@@ -1410,69 +1434,69 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3.5:1</t>
+          <t>3.4:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>+6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>+5 cmdes</t>
+          <t>-6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1481,34 +1505,34 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1.4:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1522,117 +1546,117 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
+          <t>3.3:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>3.2:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.3:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>0.2:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>-15 cmdes</t>
+          <t>4.1:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1646,19 +1670,19 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1670,17 +1694,17 @@
         <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>11.8:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
+          <t>3.5:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>-1 cmdes</t>
         </is>
@@ -1689,38 +1713,38 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>-6 cmdes</t>
+          <t>3.7:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1732,19 +1756,19 @@
         <v>4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1.6:1</t>
+          <t>3.1:1</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1760,231 +1784,262 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>4.2:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>+2 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>0.1:1</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>3.2:1</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>-17 cmdes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>AGENCE MAROUA</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>4.9:1</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>nouveau</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>-37 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>-25 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>63%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>64%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.0:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 82 cmdes soja). Comparaison vs 31/07 (bilan juillet complet).</t>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.7:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 94 cmdes soja). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2071,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 04/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2080,29 +2135,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127639</t>
+          <t>SO2608-127832</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00171 -  MME NGOBOU SOREL</t>
+          <t>CU2407-01014 -  ETS FORCE N</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2121,22 +2176,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127546</t>
+          <t>SO2608-127829</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00314 -  NZOUANKEU MANGA EPSE FOSSO</t>
+          <t>CU2407-00956 -  KOM BLAISE STANISLAS</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -2162,12 +2217,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127644</t>
+          <t>SO2608-127843</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00172 -  ONG CARESCA</t>
+          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2203,22 +2258,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127704</t>
+          <t>SO2608-127911</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2509-14122 -  CORART FARM (tchamokouen cheping arthur Rodrigue)</t>
+          <t>CU2604-14454 -  DACOSTA POULTRY FARM (JETIMONEH OLIVER NKATOH)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -2244,17 +2299,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127487</t>
+          <t>SO2608-127749</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -2285,7 +2340,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127584</t>
+          <t>SO2608-127884</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2304,10 +2359,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2326,22 +2381,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127613</t>
+          <t>SO2608-127753</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -2367,22 +2422,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127648</t>
+          <t>SO2608-127849</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -2408,29 +2463,29 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127653</t>
+          <t>SO2608-127856</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -2449,17 +2504,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127680</t>
+          <t>SO2608-127895</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2468,10 +2523,10 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -2485,320 +2540,33 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127476</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127529</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Pk11</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127552</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 10 cmdes (5.2 t) le 05/08/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127562</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127566</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127654</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-127670</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Nkolbisson</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>124</v>
-      </c>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 17 cmdes (6.2 t) le 04/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2836,7 +2604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→04/08/2026 deduites du stock. Mise a jour 04/08/2026.</t>
+          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→06/08/2026 deduites du stock. Mise a jour 06/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2879,22 +2647,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3276</v>
+        <v>2631</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>163.8</v>
+        <v>131.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>+17 jours vs 04/09/2026</t>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>+27 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2905,22 +2673,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3931</v>
+        <v>3157</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>196.5</v>
+        <v>157.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>+14 jours vs 29/08/2026</t>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+22 jours vs 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -2931,27 +2699,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2621</v>
+        <v>2105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>131</v>
+        <v>105.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>+21 jours vs 14/09/2026</t>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>+33 jours vs 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2977,34 +2745,34 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ventes post-stock 02→04/08</t>
+          <t>Ventes post-stock 02→06/08</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6 551 sacs</t>
+          <t>10 523 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>327.6 t</t>
+          <t>526.2 t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Stock restant au 04/08</t>
+          <t>Stock restant au 06/08</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>153 449 sacs</t>
+          <t>149 477 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>7672.4 t</t>
+          <t>7473.8 t</t>
         </is>
       </c>
     </row>
@@ -3016,7 +2784,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2 j (lun-sam)</t>
+          <t>4 j (lun-sam)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -3029,12 +2797,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3 275 sacs</t>
+          <t>2 630 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>163.8 t</t>
+          <t>131.5 t</t>
         </is>
       </c>
     </row>
@@ -3046,12 +2814,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>9 237 sacs</t>
+          <t>13 509 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>461.9 t</t>
+          <t>675.4 t</t>
         </is>
       </c>
     </row>
@@ -3071,35 +2839,35 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 04/08/2026 = 153 449 sacs (7672.4 t).</t>
+          <t>ANALYSE: Stock restant au 06/08/2026 = 149 477 sacs (7473.8 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Baisse moy/jour post-stock (-39.4 t/j) — effet possible de la hausse de prix.</t>
+          <t>Baisse moy/jour post-stock (-71.6 t/j) — effet possible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Seules les ventes 02→04/08 (post-stock) sont deduites du stock pour calculer le stock restant au 04/08.</t>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Seules les ventes 02→06/08 (post-stock) sont deduites du stock pour calculer le stock restant au 06/08.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 28/09/2026 (47 jours de stock restant).</t>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 12/10/2026 (57 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -3114,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3136,7 +2904,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 04/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 06/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3192,41 +2960,41 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>134.3</v>
+        <v>149.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>48.4</v>
+        <v>53.8</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.77:1</t>
+          <t>2.78:1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3247,18 +3015,18 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>255.5</v>
+        <v>266.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>91.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
+          <t>2.77:1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="8">
@@ -3276,57 +3044,115 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>130.6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>35.8</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.01:1</t>
+          <t>2.46:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2.68:1</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2.88:1</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 05-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 05-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 06-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 06-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -161,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,7 +177,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -927,14 +926,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>209.1</v>
+        <v>225.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>41.8</v>
+        <v>45.1</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-31.7 t/j</t>
+          <t>-28.4 t/j</t>
         </is>
       </c>
     </row>
@@ -950,67 +949,67 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>94.59999999999999</v>
+        <v>111</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-12.8 t/j</t>
+          <t>-9.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>61.4</v>
+        <v>66.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-45.7 t/j</t>
+          <t>-9.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>49.3</v>
+        <v>61.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.9</v>
+        <v>12.3</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-12.7 t/j</t>
+          <t>-45.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1019,67 +1018,67 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>39.1</v>
+        <v>50.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.8</v>
+        <v>10.1</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-3.4 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>35.9</v>
+        <v>48.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-9.1 t/j</t>
+          <t>-2.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>34.6</v>
+        <v>47.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-5.2 t/j</t>
+          <t>-6.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1088,67 +1087,67 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>33.8</v>
+        <v>43.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-7.0 t/j</t>
+          <t>-2.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>23.9</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-1.6 t/j</t>
+          <t>-3.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>23.8</v>
+        <v>27.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-4.4 t/j</t>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1157,14 +1156,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>22.9</v>
+        <v>26.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-1.3 t/j</t>
+          <t>-1.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1180,14 +1179,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20.8</v>
+        <v>22.4</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-1.6 t/j</t>
+          <t>-1.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1203,14 +1202,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>11.3</v>
+        <v>15.9</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-8.8 t/j</t>
+          <t>-7.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1226,14 +1225,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>-0.6 t/j</t>
+        <v>3</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1272,10 +1271,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>339.5</v>
+        <v>383.6</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>67.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1291,10 +1290,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>177.8</v>
+        <v>227.7</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>35.6</v>
+        <v>45.5</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1310,10 +1309,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>154.1</v>
+        <v>180.3</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>30.8</v>
+        <v>36.1</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1325,14 +1324,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>675.4</v>
+        <v>795.7</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>135.1</v>
+        <v>159.1</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-145.1 t/j vs 280.2</t>
+          <t>-121.1 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1345,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 135.1 t/j (2701 sacs) sur 5j.</t>
+          <t>Moyenne/jour globale: 159.1 t/j (3182 sacs) sur 5j.</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1383,7 +1382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 05/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 06/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1433,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1443,29 +1442,29 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
+          <t>1.7:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+6 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1474,65 +1473,65 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>-6 cmdes</t>
+          <t>+11 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1546,19 +1545,19 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>3.3:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1567,53 +1566,53 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
+          <t>4.0:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1628,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>4.1:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1660,146 +1659,146 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>3.4:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>-6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>3.5:1</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>3.7:1</t>
+          <t>3.2:1</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>3.1:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
+          <t>1.7:1</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
@@ -1815,231 +1814,169 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1.6:1</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>-17 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>AGENCE MAROUA</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>4.9:1</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>-40 cmdes vs 119</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>-25 cmdes vs 119</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>65%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3-5:1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>30%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>4%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>10-20:1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
           <t>0%</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.3:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.7:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 94 cmdes soja). Comparaison vs 31/07 (bilan juillet complet).</t>
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 79 cmdes soja). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2008,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 05/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2135,29 +2072,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127832</t>
+          <t>SO2608-128002</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-01014 -  ETS FORCE N</t>
+          <t>CU2508-13437 -  TEKWE MARIE LOUISE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2176,29 +2113,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127829</t>
+          <t>SO2608-127933</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00956 -  KOM BLAISE STANISLAS</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2217,29 +2154,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127843</t>
+          <t>SO2608-127986</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2258,17 +2195,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127911</t>
+          <t>SO2608-127955</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2604-14454 -  DACOSTA POULTRY FARM (JETIMONEH OLIVER NKATOH)</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2277,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>20</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2299,29 +2236,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127749</t>
+          <t>SO2608-127974</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2340,29 +2277,29 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127884</t>
+          <t>SO2608-128012</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2381,29 +2318,29 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127753</t>
+          <t>SO2608-128029</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2605-14474 -  LEONARD KANG GEH (LEONARD KANG GEH)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2422,29 +2359,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127849</t>
+          <t>SO2608-128032</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2463,7 +2400,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127856</t>
+          <t>SO2608-128048</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2504,29 +2441,29 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127895</t>
+          <t>SO2608-128064</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -2550,10 +2487,10 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
@@ -2561,7 +2498,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Total soja-only: 10 cmdes (5.2 t) le 05/08/2026</t>
+          <t>Total soja-only: 10 cmdes (1.5 t) le 06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2647,22 +2584,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2631</v>
+        <v>3232</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>131.5</v>
+        <v>161.6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>+27 jours vs 04/09/2026</t>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>+16 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2673,22 +2610,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3157</v>
+        <v>3878</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>157.8</v>
+        <v>193.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>+22 jours vs 29/08/2026</t>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>+13 jours vs 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -2699,27 +2636,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2105</v>
+        <v>2586</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>105.2</v>
+        <v>129.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>+33 jours vs 14/09/2026</t>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>+19 jours vs 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2750,12 +2687,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>10 523 sacs</t>
+          <t>12 928 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>526.2 t</t>
+          <t>646.4 t</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2704,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>149 477 sacs</t>
+          <t>147 072 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>7473.8 t</t>
+          <t>7353.6 t</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2734,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2 630 sacs</t>
+          <t>3 231 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>131.5 t</t>
+          <t>161.6 t</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2751,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>13 509 sacs</t>
+          <t>15 914 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>675.4 t</t>
+          <t>795.7 t</t>
         </is>
       </c>
     </row>
@@ -2839,35 +2776,35 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 06/08/2026 = 149 477 sacs (7473.8 t).</t>
+          <t>ANALYSE: Stock restant au 06/08/2026 = 147 072 sacs (7353.6 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Baisse moy/jour post-stock (-71.6 t/j) — effet possible de la hausse de prix.</t>
+          <t>Baisse moy/jour post-stock (-41.6 t/j) — effet possible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Seules les ventes 02→06/08 (post-stock) sont deduites du stock pour calculer le stock restant au 06/08.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 12/10/2026 (57 jours de stock restant).</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 29/09/2026 (46 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -2975,26 +2912,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3015,10 +2952,10 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>266.7</v>
+        <v>273.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -3044,18 +2981,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>130.6</v>
+        <v>133.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>53</v>
+        <v>54.1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.46:1</t>
+          <t>2.47:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="9">
@@ -3073,18 +3010,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>116.7</v>
+        <v>152.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>43.5</v>
+        <v>56.6</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.68:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -3102,57 +3039,57 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.2</v>
+        <v>86.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.2</v>
+        <v>37.4</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.88:1</t>
+          <t>2.31:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 06-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 06-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 07-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 07-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -306,12 +306,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$10</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$10</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -341,12 +341,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$10</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$10</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -453,12 +453,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$10</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$10</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -883,7 +883,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 06/08/2026 (5j). Livree. lun-sam. Mise a jour 06/08/2026.</t>
+          <t>01/07 au 08/08/2026 (7j). Livree. lun-sam. Mise a jour 08/08/2026.</t>
         </is>
       </c>
     </row>
@@ -926,14 +926,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>225.3</v>
+        <v>265.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>45.1</v>
+        <v>38</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-28.4 t/j</t>
+          <t>-35.5 t/j</t>
         </is>
       </c>
     </row>
@@ -949,14 +949,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>111</v>
+        <v>122.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>22.2</v>
+        <v>17.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-9.5 t/j</t>
+          <t>-14.2 t/j</t>
         </is>
       </c>
     </row>
@@ -972,60 +972,60 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>66.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-9.2 t/j</t>
+          <t>-9.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>61.4</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-45.7 t/j</t>
+          <t>-3.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>50.6</v>
+        <v>61.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-3.6 t/j</t>
+          <t>-49.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1041,44 +1041,44 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>48.6</v>
+        <v>58.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-2.4 t/j</t>
+          <t>-3.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>47.4</v>
+        <v>56</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-6.8 t/j</t>
+          <t>-3.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1087,14 +1087,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>43.1</v>
+        <v>50.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-2.6 t/j</t>
+          <t>-6.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>30</v>
+        <v>38.4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.1 t/j</t>
+          <t>-3.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>27.8</v>
+        <v>36.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>-1.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1156,60 +1156,60 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>26.6</v>
+        <v>34.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-1.1 t/j</t>
+          <t>-1.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>22.4</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-1.3 t/j</t>
+          <t>-7.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>15.9</v>
+        <v>27.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-7.8 t/j</t>
+          <t>-1.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1225,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>14.8</v>
+        <v>25.4</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+0.1 t/j</t>
+          <t>+0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>383.6</v>
+        <v>475.1</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>76.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>227.7</v>
+        <v>286.8</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>45.5</v>
+        <v>41</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>180.3</v>
+        <v>218.6</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>36.1</v>
+        <v>31.2</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>795.7</v>
+        <v>984.4</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>159.1</v>
+        <v>140.6</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-121.1 t/j vs 280.2</t>
+          <t>-139.6 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 159.1 t/j (3182 sacs) sur 5j.</t>
+          <t>Moyenne/jour globale: 140.6 t/j (2812 sacs) sur 7j.</t>
         </is>
       </c>
     </row>
@@ -1382,14 +1382,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 06/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 07/08/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 06/08/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 08/08/2026.</t>
         </is>
       </c>
     </row>
@@ -1442,184 +1442,184 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>+11 cmdes</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>4.0:1</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1628,60 +1628,60 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>3.1:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>-6 cmdes</t>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1690,22 +1690,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
@@ -1724,17 +1724,17 @@
         <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>3.2:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
+          <t>4.1:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>+1 cmdes</t>
         </is>
@@ -1743,7 +1743,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1765,16 +1765,16 @@
           <t>2.5:1</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1783,53 +1783,53 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>0.0:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>2.3:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>-40 cmdes vs 119</t>
+          <t>-22 cmdes vs 119</t>
         </is>
       </c>
     </row>
@@ -1891,11 +1891,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>74%</t>
         </is>
       </c>
     </row>
@@ -1906,11 +1906,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>23%</t>
         </is>
       </c>
     </row>
@@ -1921,11 +1921,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
@@ -1969,14 +1969,14 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Ratio global: 2.3:1 (vs 2.6:1 le 31/07).</t>
+          <t>Ratio global: 2.6:1 (vs 2.6:1 le 31/07).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 79 cmdes soja). Comparaison vs 31/07 (bilan juillet complet).</t>
+          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 97 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2008,7 +2008,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 06/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2072,29 +2072,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128002</t>
+          <t>SO2608-128162</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2508-13437 -  TEKWE MARIE LOUISE</t>
+          <t>CU2504-01304 -  MADZU SOLANGE Epse TENE (ZDCL00030)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2113,29 +2113,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127933</t>
+          <t>SO2608-128177</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00185 -  NGNIMPEYE JEAN PIERRE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2154,29 +2154,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127986</t>
+          <t>SO2608-128263</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2407-00159 -  SIGNE WILLIAM</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2195,17 +2195,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127955</t>
+          <t>SO2608-128250</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2509-13911 -  KOMEGNE EPSE NZOCK CELESTINE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2236,29 +2236,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-127974</t>
+          <t>SO2608-128288</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2277,29 +2277,29 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128012</t>
+          <t>SO2608-128180</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2318,17 +2318,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128029</t>
+          <t>SO2608-128213</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2605-14474 -  LEONARD KANG GEH (LEONARD KANG GEH)</t>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2359,29 +2359,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128032</t>
+          <t>SO2608-128233</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2400,22 +2400,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128048</t>
+          <t>SO2608-128203</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2508-13625 -  TAGNI SADIO MAXIME</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -2441,69 +2441,315 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128064</t>
+          <t>SO2608-128179</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Djeleng</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128205</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128208</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128220</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
           <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Ngaoundere</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G14" s="4" t="n">
+      <c r="F17" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128289</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Messassi</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128111</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Messassi</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128201</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 10 cmdes (1.5 t) le 06/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 16 cmdes (6.4 t) le 07/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2541,7 +2787,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→06/08/2026 deduites du stock. Mise a jour 06/08/2026.</t>
+          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→08/08/2026 deduites du stock. Mise a jour 08/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2584,22 +2830,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3232</v>
+        <v>2784</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>161.6</v>
+        <v>139.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>+16 jours vs 04/09/2026</t>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>+21 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2610,22 +2856,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3878</v>
+        <v>3341</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>193.9</v>
+        <v>167</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>+13 jours vs 29/08/2026</t>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+18 jours vs 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -2636,22 +2882,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2586</v>
+        <v>2227</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>129.3</v>
+        <v>111.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>+19 jours vs 14/09/2026</t>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>+26 jours vs 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -2682,34 +2928,34 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ventes post-stock 02→06/08</t>
+          <t>Ventes post-stock 02→08/08</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>12 928 sacs</t>
+          <t>16 703 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>646.4 t</t>
+          <t>835.1 t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Stock restant au 06/08</t>
+          <t>Stock restant au 08/08</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>147 072 sacs</t>
+          <t>143 297 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>7353.6 t</t>
+          <t>7164.9 t</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2967,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>4 j (lun-sam)</t>
+          <t>6 j (lun-sam)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -2734,12 +2980,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3 231 sacs</t>
+          <t>2 783 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>161.6 t</t>
+          <t>139.2 t</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2997,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>15 914 sacs</t>
+          <t>19 689 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>795.7 t</t>
+          <t>984.4 t</t>
         </is>
       </c>
     </row>
@@ -2776,14 +3022,14 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 06/08/2026 = 147 072 sacs (7353.6 t).</t>
+          <t>ANALYSE: Stock restant au 08/08/2026 = 143 297 sacs (7164.9 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Baisse moy/jour post-stock (-41.6 t/j) — effet possible de la hausse de prix.</t>
+          <t>Baisse moy/jour post-stock (-64.0 t/j) — effet possible de la hausse de prix.</t>
         </is>
       </c>
     </row>
@@ -2797,14 +3043,14 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Seules les ventes 02→06/08 (post-stock) sont deduites du stock pour calculer le stock restant au 06/08.</t>
+          <t>Seules les ventes 02→08/08 (post-stock) sont deduites du stock pour calculer le stock restant au 08/08.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 29/09/2026 (46 jours de stock restant).</t>
+          <t>Date de rupture probable: 07/10/2026 (51 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -2819,7 +3065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2841,7 +3087,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 06/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 08/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2952,10 +3198,10 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>273.2</v>
+        <v>280.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>101.1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -2981,18 +3227,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>133.8</v>
+        <v>139.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>54.1</v>
+        <v>56.6</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.47:1</t>
+          <t>2.46:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="9">
@@ -3010,18 +3256,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>152.7</v>
+        <v>155.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>56.6</v>
+        <v>57.7</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>2.69:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="10">
@@ -3039,57 +3285,115 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>86.7</v>
+        <v>110.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>37.4</v>
+        <v>50.1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.31:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>2.66:1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 07-08" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 07-08" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +101,9 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -161,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +185,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -260,7 +270,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -417,7 +426,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2766,305 +2774,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→08/08/2026 deduites du stock. Mise a jour 08/08/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Sacs/jour (post-stock)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>t/jour</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Jours stock</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Date rupture</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Evolution date rupture</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Realiste</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2784</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>139.2</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>+21 jours vs 04/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Acceleration +20%</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3341</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>+18 jours vs 29/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Ralentissement -20%</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>2227</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>+26 jours vs 14/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Parametres</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Stock initial (au 21/07)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>160 000 sacs</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>8000 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Ventes post-stock 02→08/08</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>16 703 sacs</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>835.1 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Stock restant au 08/08</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>143 297 sacs</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>7164.9 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Jours ouvrables post-stock</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>6 j (lun-sam)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Moyenne/jour post-stock</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2 783 sacs</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>139.2 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Ventes août (total, info)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>19 689 sacs</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>984.4 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Hausse prix soja</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>+2 000 XAF/sac le 23/07/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Stock restant au 08/08/2026 = 143 297 sacs (7164.9 t).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Baisse moy/jour post-stock (-64.0 t/j) — effet possible de la hausse de prix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Seules les ventes 02→08/08 (post-stock) sont deduites du stock pour calculer le stock restant au 08/08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 07/10/2026 (51 jours de stock restant).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3403,4 +3112,457 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Stock physique au 08/08/2026 (magasins centraux BEKOKO). Consommation = Vente directe + Production concentrés. Mise à jour 08/08/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Nb sacs</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Poids (t)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Équivalent sacs 50kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 50kg (T102)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>80384</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4019.2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>80384</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 1kg (T1021)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 5kg (T1023)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 25kg (T1024)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>82634</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>4021.5</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>80430</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Sacs/sem (lun-sam)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Sacs/jour</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>t/sem</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Vente directe soja</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>16876</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2813</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>844</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Ventes août 7j (Livrée)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (min)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (moy)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>817</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (max)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>883</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MIN (vente + prod min)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>21376</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>3563</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>1069</v>
+      </c>
+      <c r="E18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MOY (vente + prod moy)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>21776</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>3629</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MAX (vente + prod max)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>22176</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>3696</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1109</v>
+      </c>
+      <c r="E20" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>3. DATE DE RUPTURE PROBABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Scénario</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Stock (sacs éq. 50kg)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Conso (sacs/sem)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Jours restants</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Semaines</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Date rupture</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Min (conso min)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>80430</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>21376</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Moyen (conso moy)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>80430</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>21776</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Max (conso max)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>80430</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>22176</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Le stock de 80 430 sacs (4 021 t) couvre 25-26 jours (3,6-3,8 semaines) de consommation totale (vente + production).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 02-03/09/2026. URGENGE: prévoir réapprovisionnement avant le 25/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Méthode: stock = ventes soja directes (2 813 sacs/j) + production concentrés (4 500-5 300 sacs/sem).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Le stock inclut tous les formats: 50kg, 1kg, 5kg, 25kg (convertis en équivalent 50kg).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 07-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 07-08" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 08-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 08-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -104,8 +104,11 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -137,6 +140,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -164,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,11 +193,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -315,12 +323,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$12</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$12</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +358,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$12</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$12</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -461,12 +469,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$12</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$12</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -891,7 +899,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 08/08/2026 (7j). Livree. lun-sam. Mise a jour 08/08/2026.</t>
+          <t>01/07 au 10/08/2026 (8j). Livree. lun-sam. Mise a jour 10/08/2026.</t>
         </is>
       </c>
     </row>
@@ -934,14 +942,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>265.7</v>
+        <v>276</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>38</v>
+        <v>34.5</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-35.5 t/j</t>
+          <t>-39.0 t/j</t>
         </is>
       </c>
     </row>
@@ -957,14 +965,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>122.8</v>
+        <v>145.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-14.2 t/j</t>
+          <t>-13.6 t/j</t>
         </is>
       </c>
     </row>
@@ -980,14 +988,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.7</v>
+        <v>11.2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-9.9 t/j</t>
+          <t>-11.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1011,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-3.9 t/j</t>
+          <t>-5.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1026,67 +1034,67 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>61.4</v>
+        <v>74.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-49.2 t/j</t>
+          <t>-48.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>58.1</v>
+        <v>62.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-3.8 t/j</t>
+          <t>-6.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>56</v>
+        <v>60.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-3.2 t/j</t>
+          <t>-4.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1095,14 +1103,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>50.9</v>
+        <v>56.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-6.5 t/j</t>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1118,21 +1126,21 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>38.4</v>
+        <v>44.3</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>5.5</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.7 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1141,21 +1149,21 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>36.7</v>
+        <v>40.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-1.1 t/j</t>
+          <t>-0.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1164,21 +1172,21 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>34.3</v>
+        <v>38.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-1.0 t/j</t>
+          <t>-6.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1187,14 +1195,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>28</v>
+        <v>37.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-7.0 t/j</t>
+          <t>-1.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1218,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>27.6</v>
+        <v>30.5</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-1.9 t/j</t>
+          <t>-2.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1241,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>25.4</v>
+        <v>26.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+0.8 t/j</t>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1267,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1279,10 +1287,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>475.1</v>
+        <v>509.1</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>67.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1298,10 +1306,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>286.8</v>
+        <v>310.1</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>41</v>
+        <v>38.8</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1317,10 +1325,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>218.6</v>
+        <v>251.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1332,14 +1340,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>984.4</v>
+        <v>1074.4</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>140.6</v>
+        <v>134.3</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-139.6 t/j vs 280.2</t>
+          <t>-145.9 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1361,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 140.6 t/j (2812 sacs) sur 7j.</t>
+          <t>Moyenne/jour globale: 134.3 t/j (2685 sacs) sur 8j.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1390,14 +1398,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 07/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 08/08/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 08/08/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 10/08/2026.</t>
         </is>
       </c>
     </row>
@@ -1450,22 +1458,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>2.9:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1502,7 @@
           <t>2.6:1</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>+4 cmdes</t>
         </is>
@@ -1503,38 +1511,38 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1543,22 +1551,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
@@ -1574,60 +1582,60 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>1.5:1</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1636,60 +1644,60 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.1:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>0.9:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>-13 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1698,60 +1706,60 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>4.1:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1760,29 +1768,29 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>8.1:1</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1801,146 +1809,130 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>0.0:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Ahala</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>4.0:1</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>-22 cmdes vs 119</t>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>-57 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>4%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -1952,39 +1944,24 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.6:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 97 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.4:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2016,7 +1993,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 07/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 08/08/2026</t>
         </is>
       </c>
     </row>
@@ -2080,29 +2057,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128162</t>
+          <t>SO2608-128420</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2504-01304 -  MADZU SOLANGE Epse TENE (ZDCL00030)</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.5</v>
+        <v>0.15</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2121,29 +2098,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128177</t>
+          <t>SO2608-128293</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00185 -  NGNIMPEYE JEAN PIERRE</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2162,29 +2139,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128263</t>
+          <t>SO2608-128299</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00159 -  SIGNE WILLIAM</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2203,17 +2180,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128250</t>
+          <t>SO2608-128315</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2509-13911 -  KOMEGNE EPSE NZOCK CELESTINE</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2222,10 +2199,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2244,29 +2221,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128288</t>
+          <t>SO2608-128371</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2285,29 +2262,29 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128180</t>
+          <t>SO2608-128337</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2508-13748 -  MBAMBAPRI BENADETTE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2326,29 +2303,29 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128213</t>
+          <t>SO2608-128368</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2367,17 +2344,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128233</t>
+          <t>SO2608-128387</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00741 -  LONTSI OSCAR</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2386,10 +2363,10 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2403,361 +2380,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128203</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CU2508-13625 -  TAGNI SADIO MAXIME</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128179</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128205</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 8 cmdes (0.7 t) le 08/08/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128208</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128220</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128289</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Messassi</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128111</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Messassi</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128201</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 16 cmdes (6.4 t) le 07/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2774,7 +2423,493 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Stock physique au 08/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs alloués SPC. Mise à jour 10/08/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Nb sacs</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Poids (t)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Équivalent sacs 50kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 50kg (T102)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>80384</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4019.2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>80384</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 1kg (T1021)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 5kg (T1023)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 25kg (T1024)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>STOCK BRUT TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>82634</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>4021.5</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>80430</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Moins: allocation SPC (entité soeur)</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>460</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>STOCK NET DISPONIBLE BELGOCAM</t>
+        </is>
+      </c>
+      <c r="B12" s="22">
+        <f>73434 (sacs réels)</f>
+        <v/>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>3561.5</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>71230</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Sacs/sem (lun-sam)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Sacs/jour</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>t/sem</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Vente directe soja</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>16115</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>2686</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>806</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Ventes août 8j (Livrée)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (min)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (moy)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>817</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (max)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>883</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MIN (vente + prod min)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>20615</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>3436</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MOY (vente + prod moy)</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>21015</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>3503</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>1051</v>
+      </c>
+      <c r="E21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MAX (vente + prod max)</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>21415</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>3569</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1071</v>
+      </c>
+      <c r="E22" s="23" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net disponible BELGOCAM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Scénario</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Stock net (sacs éq. 50kg)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Conso (sacs/sem)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Jours restants</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Semaines</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Date rupture</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Min (conso min)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>20615</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Moyen (conso moy)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>21015</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Max (conso max)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>21415</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock net BELGOCAM = 71230 sacs (3561 t) après exclusion 9 200 sacs SPC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 02/09/2026 (23 jours, 3.4 semaines).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 23/08/2026 (10 jours de marge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4 500-5 300 sacs/sem).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2796,7 +2931,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 08/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 10/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2907,18 +3042,18 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>280.2</v>
+        <v>282.1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>101.1</v>
+        <v>102.1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.77:1</t>
+          <t>2.76:1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="8">
@@ -2936,18 +3071,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>139.3</v>
+        <v>146.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>56.6</v>
+        <v>59</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.46:1</t>
+          <t>2.48:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="9">
@@ -2965,18 +3100,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>155.2</v>
+        <v>166.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>57.7</v>
+        <v>61.6</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.69:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -2994,18 +3129,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>110.1</v>
+        <v>117.6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>50.1</v>
+        <v>52.8</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>2.23:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="11">
@@ -3023,18 +3158,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>121.1</v>
+        <v>137.6</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>46.5</v>
+        <v>51.9</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>2.65:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="12">
@@ -3052,57 +3187,109 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>29.2</v>
+        <v>75.2</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>11</v>
+        <v>31.7</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.66:1</t>
+          <t>2.37:1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>
@@ -3112,457 +3299,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Stock physique au 08/08/2026 (magasins centraux BEKOKO). Consommation = Vente directe + Production concentrés. Mise à jour 08/08/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Nb sacs</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Poids (t)</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Équivalent sacs 50kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 50kg (T102)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>80384</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4019.2</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>80384</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 1kg (T1021)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>2245</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 5kg (T1023)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 25kg (T1024)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>82634</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>4021.5</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>80430</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Flux</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Sacs/sem (lun-sam)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>Sacs/jour</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>t/sem</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Vente directe soja</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>16876</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2813</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>844</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Ventes août 7j (Livrée)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (min)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (moy)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>4900</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>817</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (max)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>883</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MIN (vente + prod min)</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>21376</v>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>3563</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>1069</v>
-      </c>
-      <c r="E18" s="21" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MOY (vente + prod moy)</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>21776</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>3629</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>1089</v>
-      </c>
-      <c r="E19" s="21" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MAX (vente + prod max)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>22176</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>3696</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>1109</v>
-      </c>
-      <c r="E20" s="21" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>3. DATE DE RUPTURE PROBABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Scénario</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Stock (sacs éq. 50kg)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>Conso (sacs/sem)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>Jours restants</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>Semaines</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>Date rupture</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Min (conso min)</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>80430</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>21376</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Moyen (conso moy)</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>80430</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>21776</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Max (conso max)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>80430</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>22176</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Le stock de 80 430 sacs (4 021 t) couvre 25-26 jours (3,6-3,8 semaines) de consommation totale (vente + production).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 02-03/09/2026. URGENGE: prévoir réapprovisionnement avant le 25/08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>Méthode: stock = ventes soja directes (2 813 sacs/j) + production concentrés (4 500-5 300 sacs/sem).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Le stock inclut tous les formats: 50kg, 1kg, 5kg, 25kg (convertis en équivalent 50kg).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 08-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 08-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 10-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 10-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,10 +77,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
@@ -101,14 +106,8 @@
     <font>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00C00000"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -140,11 +139,6 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -172,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,18 +182,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -278,6 +266,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -434,6 +423,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -942,14 +932,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>276</v>
+        <v>344.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>34.5</v>
+        <v>43</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-39.0 t/j</t>
+          <t>-30.5 t/j</t>
         </is>
       </c>
     </row>
@@ -965,14 +955,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>145.2</v>
+        <v>167.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>18.1</v>
+        <v>20.9</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-13.6 t/j</t>
+          <t>-10.8 t/j</t>
         </is>
       </c>
     </row>
@@ -988,14 +978,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>132.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11.2</v>
+        <v>16.6</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-11.3 t/j</t>
+          <t>-6.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1011,14 +1001,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-5.3 t/j</t>
+          <t>-3.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1048,46 +1038,46 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>62.5</v>
+        <v>73.3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-6.0 t/j</t>
+          <t>-2.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>60.1</v>
+        <v>71.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-4.6 t/j</t>
+          <t>-4.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1103,44 +1093,44 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>56.3</v>
+        <v>61.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.2 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>44.3</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.6 t/j</t>
+          <t>-5.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1149,44 +1139,44 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>40.3</v>
+        <v>45.4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.9 t/j</t>
+          <t>-0.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>38.3</v>
+        <v>44.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-6.2 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1195,14 +1185,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>37.9</v>
+        <v>40.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-1.6 t/j</t>
+          <t>-0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1208,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>30.5</v>
+        <v>35.9</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-2.0 t/j</t>
+          <t>-1.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1231,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>26.7</v>
+        <v>29.1</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+0.5 t/j</t>
+          <t>+0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1264,10 +1254,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1287,10 +1277,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>509.1</v>
+        <v>610.6</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>63.6</v>
+        <v>76.3</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1306,10 +1296,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>310.1</v>
+        <v>375.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>38.8</v>
+        <v>46.9</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1325,10 +1315,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>251.2</v>
+        <v>280.6</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>31.4</v>
+        <v>35.1</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1340,14 +1330,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>1074.4</v>
+        <v>1280.4</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>134.3</v>
+        <v>160.1</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-145.9 t/j vs 280.2</t>
+          <t>-120.2 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1351,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 134.3 t/j (2685 sacs) sur 8j.</t>
+          <t>Moyenne/jour globale: 160.1 t/j (3201 sacs) sur 8j.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1388,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 08/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 10/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1458,60 +1448,60 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>+27 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1520,60 +1510,60 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>3.8:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>+5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1582,29 +1572,29 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.3:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1613,29 +1603,29 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>1.8:1</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1644,29 +1634,29 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>0.9:1</t>
+          <t>1.0:1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1675,51 +1665,51 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>-13 cmdes</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>+1 cmdes</t>
         </is>
@@ -1728,93 +1718,93 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>8.1:1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>AGENCE MAROUA</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>?</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
@@ -1826,13 +1816,13 @@
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -1841,12 +1831,12 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>-57 cmdes vs 119</t>
+          <t>+21 cmdes vs 119</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
@@ -1876,7 +1866,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1891,11 +1881,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>21%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1900,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1949,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1976,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1993,7 +1983,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 08/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2057,29 +2047,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128420</t>
+          <t>SO2608-128516</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00872 -  NKUE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.15</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2098,29 +2088,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128293</t>
+          <t>SO2608-128626</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2608-14582 -  SPS MAROUA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>AGENCE MAROUA</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>?</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2139,17 +2129,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128299</t>
+          <t>SO2608-128474</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2501-01190 -  ETS GRAND ELEVEUR (NGONGANG KENMOE)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2158,10 +2148,10 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2180,29 +2170,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128315</t>
+          <t>SO2608-128468</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00722 -  KUE FOTSO ARNAULO</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2221,29 +2211,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128371</t>
+          <t>SO2608-128511</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00168 -  KAMGNO PIERRE</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2262,17 +2252,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128337</t>
+          <t>SO2608-128507</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2508-13748 -  MBAMBAPRI BENADETTE</t>
+          <t>CU2407-00875 -  NOUMSI BLAISE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2281,10 +2271,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2303,17 +2293,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128368</t>
+          <t>SO2608-128645</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2322,10 +2312,10 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2344,12 +2334,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128387</t>
+          <t>SO2608-128463</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00741 -  LONTSI OSCAR</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2363,50 +2353,665 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128495</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128510</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128528</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128669</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Djeleng</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128554</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128440</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00175 -  CLIENT COMPTOIR NKONGSSAMBA</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Nkongsamba</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128499</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128536</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128579</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128586</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128602</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128606</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00175 -  CLIENT COMPTOIR NKONGSSAMBA</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Nkongsamba</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128614</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128649</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>CU2508-13571 -  TALLA TESSO MEFENYA TIBEAU</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-128643</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 8 cmdes (0.7 t) le 08/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>298</v>
+      </c>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 23 cmdes (14.9 t) le 10/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2423,478 +3028,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
+          <t>TABLEAU 4 - Stock SOJA et date rupture</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 08/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs alloués SPC. Mise à jour 10/08/2026.</t>
+          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→10/08/2026 deduites du stock. Mise a jour 10/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sacs/jour (post-stock)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>t/jour</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Jours stock</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Date rupture</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Evolution date rupture</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Nb sacs</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Poids (t)</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Équivalent sacs 50kg</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Realiste</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3207</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>+13 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Sacs de 50kg (T102)</t>
+          <t>Acceleration +20%</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>80384</v>
+        <v>3849</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4019.2</v>
+        <v>192.4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>80384</v>
+        <v>36</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+11 jours vs 29/08/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Sacs de 1kg (T1021)</t>
+          <t>Ralentissement -20%</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2245</v>
+        <v>2566</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.245</v>
+        <v>128.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 5kg (T1023)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.4</v>
+        <v>54</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>+16 jours vs 14/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 25kg (T1024)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.5</v>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Parametres</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>STOCK BRUT TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>82634</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>4021.5</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>80430</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Stock initial (au 21/07)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>160 000 sacs</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>8000 t</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Moins: allocation SPC (entité soeur)</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>9200</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>460</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>9200</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Ventes post-stock 02→10/08</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>22 452 sacs</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1122.6 t</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>STOCK NET DISPONIBLE BELGOCAM</t>
-        </is>
-      </c>
-      <c r="B12" s="22">
-        <f>73434 (sacs réels)</f>
-        <v/>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>71230</v>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Stock restant au 10/08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>137 548 sacs</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>6877.4 t</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Jours ouvrables post-stock</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>7 j (lun-sam)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Moyenne/jour post-stock</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>3 207 sacs</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>160.4 t</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Flux</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Sacs/sem (lun-sam)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Sacs/jour</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>t/sem</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ventes août (total, info)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>25 608 sacs</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1280.4 t</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Vente directe soja</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>16115</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2686</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>806</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Ventes août 8j (Livrée)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (min)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (moy)</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>4900</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>817</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
+          <t>Hausse prix soja</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>+2 000 XAF/sac le 23/07/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (max)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>883</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock restant au 10/08/2026 = 137 548 sacs (6877.4 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MIN (vente + prod min)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>20615</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>3436</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E20" s="23" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Baisse moy/jour post-stock (-42.8 t/j) — effet possible de la hausse de prix.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MOY (vente + prod moy)</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>21015</v>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>3503</v>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>1051</v>
-      </c>
-      <c r="E21" s="23" t="n"/>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MAX (vente + prod max)</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>21415</v>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>3569</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>1071</v>
-      </c>
-      <c r="E22" s="23" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net disponible BELGOCAM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Scénario</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Stock net (sacs éq. 50kg)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Conso (sacs/sem)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Jours restants</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>Semaines</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>Date rupture</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Min (conso min)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>71230</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>20615</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Moyen (conso moy)</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>71230</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>21015</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Max (conso max)</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>71230</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>21415</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Stock net BELGOCAM = 71230 sacs (3561 t) après exclusion 9 200 sacs SPC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 02/09/2026 (23 jours, 3.4 semaines).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 23/08/2026 (10 jours de marge).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4 500-5 300 sacs/sem).</t>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Seules les ventes 02→10/08 (post-stock) sont deduites du stock pour calculer le stock restant au 10/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 29/09/2026 (43 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -2987,10 +3405,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>149.3</v>
+        <v>150.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -3002,26 +3420,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3074,7 +3492,7 @@
         <v>146.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -3129,18 +3547,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>117.6</v>
+        <v>122.5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>52.8</v>
+        <v>54.6</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.23:1</t>
+          <t>2.24:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="11">
@@ -3158,7 +3576,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>137.6</v>
+        <v>137.7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>51.9</v>
@@ -3187,41 +3605,41 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>75.2</v>
+        <v>90.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>31.7</v>
+        <v>36.7</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.37:1</t>
+          <t>2.47:1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3242,54 +3660,57 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0</v>
+        <v>177.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>73.2</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>2.42:1</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2.42</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 10-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 10-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 11-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 11-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,11 +82,6 @@
     </font>
     <font>
       <color rgb="00008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -166,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,12 +177,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -932,14 +926,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>344.4</v>
+        <v>390.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>43</v>
+        <v>48.8</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-30.5 t/j</t>
+          <t>-24.7 t/j</t>
         </is>
       </c>
     </row>
@@ -955,14 +949,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>167.2</v>
+        <v>216.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.9</v>
+        <v>27.1</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-10.8 t/j</t>
+          <t>-4.6 t/j</t>
         </is>
       </c>
     </row>
@@ -978,14 +972,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>132.6</v>
+        <v>152.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-6.0 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1001,14 +995,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>99.2</v>
+        <v>115.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-3.9 t/j</t>
+          <t>-1.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1018,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>74.5</v>
+        <v>102.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-48.6 t/j</t>
+          <t>-45.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1047,14 +1041,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>73.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-2.9 t/j</t>
+          <t>-2.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1064,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>71.8</v>
+        <v>80.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-4.8 t/j</t>
+          <t>-3.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1087,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>61.5</v>
+        <v>79.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-3.6 t/j</t>
+          <t>-1.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1116,60 +1110,60 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>47</v>
+        <v>60.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-5.1 t/j</t>
+          <t>-3.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>45.4</v>
+        <v>57</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.7 t/j</t>
+          <t>-2.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>44.3</v>
+        <v>50.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>-3.6 t/j</t>
+        <v>6.3</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1179,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>40.3</v>
+        <v>44.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-0.9 t/j</t>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1208,14 +1202,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>35.9</v>
+        <v>37.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-1.3 t/j</t>
+          <t>-1.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1277,10 +1271,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>610.6</v>
+        <v>722.3</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>76.3</v>
+        <v>90.3</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1296,10 +1290,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>375.2</v>
+        <v>435.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>46.9</v>
+        <v>54.4</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1315,10 +1309,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>280.6</v>
+        <v>339.8</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>35.1</v>
+        <v>42.5</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1330,14 +1324,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>1280.4</v>
+        <v>1511.3</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>160.1</v>
+        <v>188.9</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-120.2 t/j vs 280.2</t>
+          <t>-91.3 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1345,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 160.1 t/j (3201 sacs) sur 8j.</t>
+          <t>Moyenne/jour globale: 188.9 t/j (3778 sacs) sur 8j.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1388,7 +1382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 10/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 11/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1433,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1448,96 +1442,96 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+27 cmdes</t>
+          <t>+6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>-10 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3.8:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>+5 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1551,24 +1545,24 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -1582,81 +1576,81 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
+          <t>1.1:1</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1.0:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>+7 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1665,22 +1659,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.8:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
@@ -1696,53 +1690,53 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
@@ -1758,171 +1752,203 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1.0:1</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>0.1:1</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>AGENCE MAROUA</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>-8 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Pk11</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1.8:1</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>2.4:1</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>+21 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>-29 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>3-5:1</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>21%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>&gt; 20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -1934,22 +1960,52 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 20:1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Ratio global: 2.4:1 (vs 2.6:1 le 31/07).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1966,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1983,7 +2039,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 10/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2047,29 +2103,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128516</t>
+          <t>SO2608-128843</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00872 -  NKUE</t>
+          <t>CU2501-01196 -  SCOOPS MOUNGO (MR NKENGUE VALENTIN)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2088,29 +2144,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128626</t>
+          <t>SO2608-128871</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2608-14582 -  SPS MAROUA</t>
+          <t>CU2407-00162 -  FOTSING PIERRE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AGENCE MAROUA</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2129,29 +2185,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128474</t>
+          <t>SO2608-128820</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2501-01190 -  ETS GRAND ELEVEUR (NGONGANG KENMOE)</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.5</v>
+        <v>0.15</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2170,29 +2226,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128468</t>
+          <t>SO2608-128834</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00722 -  KUE FOTSO ARNAULO</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2211,17 +2267,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128511</t>
+          <t>SO2608-128756</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00168 -  KAMGNO PIERRE</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -2230,10 +2286,10 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>20</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2252,12 +2308,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128507</t>
+          <t>SO2608-128764</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00875 -  NOUMSI BLAISE</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2271,11 +2327,11 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
@@ -2288,730 +2344,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128645</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Nkongsamba</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128463</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128495</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 6 cmdes (2.4 t) le 11/08/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128510</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128528</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128669</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128554</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128440</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00175 -  CLIENT COMPTOIR NKONGSSAMBA</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Nkongsamba</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128499</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128536</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128579</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128586</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128602</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128606</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00175 -  CLIENT COMPTOIR NKONGSSAMBA</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Nkongsamba</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128614</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128649</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>CU2508-13571 -  TALLA TESSO MEFENYA TIBEAU</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128643</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>298</v>
-      </c>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 23 cmdes (14.9 t) le 10/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -3092,22 +2451,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3207</v>
+        <v>3518</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>160.4</v>
+        <v>175.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>+13 jours vs 04/09/2026</t>
+          <t>+8 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3118,22 +2477,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3849</v>
+        <v>4221</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>192.4</v>
+        <v>211.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>+11 jours vs 29/08/2026</t>
+          <t>+7 jours vs 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -3144,27 +2503,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2566</v>
+        <v>2814</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>128.3</v>
+        <v>140.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>+16 jours vs 14/09/2026</t>
+          <t>+10 jours vs 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -3195,12 +2554,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>22 452 sacs</t>
+          <t>24 625 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1122.6 t</t>
+          <t>1231.3 t</t>
         </is>
       </c>
     </row>
@@ -3212,12 +2571,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>137 548 sacs</t>
+          <t>135 375 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6877.4 t</t>
+          <t>6768.7 t</t>
         </is>
       </c>
     </row>
@@ -3242,12 +2601,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3 207 sacs</t>
+          <t>3 517 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>160.4 t</t>
+          <t>175.9 t</t>
         </is>
       </c>
     </row>
@@ -3259,12 +2618,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>25 608 sacs</t>
+          <t>30 226 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>1280.4 t</t>
+          <t>1511.3 t</t>
         </is>
       </c>
     </row>
@@ -3284,35 +2643,35 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 10/08/2026 = 137 548 sacs (6877.4 t).</t>
+          <t>ANALYSE: Stock restant au 10/08/2026 = 135 375 sacs (6768.7 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Baisse moy/jour post-stock (-42.8 t/j) — effet possible de la hausse de prix.</t>
+          <t>Baisse moy/jour post-stock (-27.3 t/j) — effet possible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Seules les ventes 02→10/08 (post-stock) sont deduites du stock pour calculer le stock restant au 10/08.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 29/09/2026 (43 jours de stock restant).</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 23/09/2026 (38 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -3420,26 +2779,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3460,18 +2819,18 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>282.1</v>
+        <v>288.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>102.1</v>
+        <v>104.4</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.76:1</t>
+          <t>2.77:1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="8">
@@ -3489,18 +2848,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>146.3</v>
+        <v>151.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>59.1</v>
+        <v>60.5</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.48:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -3518,18 +2877,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>166.2</v>
+        <v>174.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>61.6</v>
+        <v>65.2</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>2.68:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="10">
@@ -3576,18 +2935,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>137.7</v>
+        <v>144.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>51.9</v>
+        <v>54.1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.65:1</t>
+          <t>2.67:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="12">
@@ -3605,41 +2964,41 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>90.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>36.7</v>
+        <v>38.8</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.47:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3660,57 +3019,57 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>177.1</v>
+        <v>252.8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>73.2</v>
+        <v>101.7</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.42:1</t>
+          <t>2.49:1</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,8 +101,14 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +140,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -161,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +193,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -260,7 +279,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -417,7 +435,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2387,291 +2404,482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture</t>
+          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→10/08/2026 deduites du stock. Mise a jour 10/08/2026.</t>
+          <t>Stock physique au 08/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs alloués SPC. Consommation = Vente + Production conc. Mise à jour 12/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Sacs/jour (post-stock)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>t/jour</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Jours stock</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Date rupture</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Evolution date rupture</t>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Realiste</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>3518</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>+8 jours vs 04/09/2026</t>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Nb sacs</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Poids (t)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Équivalent sacs 50kg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Acceleration +20%</t>
+          <t>Sacs de 50kg (T102)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4221</v>
+        <v>80384</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>211.1</v>
+        <v>4019.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>+7 jours vs 29/08/2026</t>
-        </is>
+        <v>80384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ralentissement -20%</t>
+          <t>Sacs de 1kg (T1021)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2814</v>
+        <v>2245</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>140.7</v>
+        <v>2.245</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>+10 jours vs 14/09/2026</t>
-        </is>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 5kg (T1023)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Parametres</t>
-        </is>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 25kg (T1024)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Stock initial (au 21/07)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>160 000 sacs</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>8000 t</t>
-        </is>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>STOCK BRUT TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>82634</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>4021.5</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>80430</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Ventes post-stock 02→10/08</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>24 625 sacs</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>1231.3 t</t>
-        </is>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Moins: allocation SPC (entité soeur)</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>460</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>9200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Stock restant au 10/08</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>135 375 sacs</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>6768.7 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Jours ouvrables post-stock</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>7 j (lun-sam)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>STOCK NET DISPONIBLE BELGOCAM</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="23" t="n">
+        <v>3561.5</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>71230</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Moyenne/jour post-stock</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>3 517 sacs</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>175.9 t</t>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Ventes août (total, info)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>30 226 sacs</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>1511.3 t</t>
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Sacs/sem (lun-sam)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Sacs/jour</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>t/sem</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Hausse prix soja</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>+2 000 XAF/sac le 23/07/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
+          <t>Vente directe soja</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>20117</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Ventes août 9j (Livrée, 12/08 exclu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (min)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (moy)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>817</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Stock restant au 10/08/2026 = 135 375 sacs (6768.7 t).</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (max)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>883</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Baisse moy/jour post-stock (-27.3 t/j) — effet possible de la hausse de prix.</t>
-        </is>
-      </c>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MIN (vente + prod min)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>24617</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>4103</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MOY (vente + prod moy)</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>25017</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>4170</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>1251</v>
+      </c>
+      <c r="E21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Seules les ventes 02→10/08 (post-stock) sont deduites du stock pour calculer le stock restant au 10/08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 23/09/2026 (38 jours de stock restant).</t>
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MAX (vente + prod max)</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>25417</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>4236</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1271</v>
+      </c>
+      <c r="E22" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net disponible BELGOCAM, départ 11/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Scénario</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Stock net (sacs éq. 50kg)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Conso (sacs/sem)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Jours restants</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Semaines</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Date rupture</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Min (conso min)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>24617</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Moyen (conso moy)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>25017</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Max (conso max)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>25417</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock net BELGOCAM = 71230 sacs (3561 t) après exclusion 9 200 sacs SPC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 30/08/2026 (19 jours, 2.8 semaines).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 20/08/2026 (10 jours de marge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4 500-5 300 sacs/sem).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 11/08 (9j, 12/08 matinal exclu).</t>
         </is>
       </c>
     </row>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 11-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 11-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 13-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 13-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,14 +101,8 @@
     <font>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00C00000"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -140,11 +134,6 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -172,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,14 +182,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,6 +260,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -435,6 +417,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -943,14 +926,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>390.4</v>
+        <v>429.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>48.8</v>
+        <v>53.7</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-24.7 t/j</t>
+          <t>-19.8 t/j</t>
         </is>
       </c>
     </row>
@@ -966,14 +949,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>216.8</v>
+        <v>243.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>27.1</v>
+        <v>30.4</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-4.6 t/j</t>
+          <t>-1.3 t/j</t>
         </is>
       </c>
     </row>
@@ -989,14 +972,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>152.1</v>
+        <v>222.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>-3.5 t/j</t>
+        <v>27.8</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>+5.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1012,14 +995,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>115.2</v>
+        <v>130.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-1.9 t/j</t>
+        <v>16.3</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1035,44 +1018,44 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>102.9</v>
+        <v>120.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12.9</v>
+        <v>15</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-45.1 t/j</t>
+          <t>-42.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>109</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10.1</v>
+        <v>13.6</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-2.0 t/j</t>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1081,37 +1064,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>80.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>-3.7 t/j</t>
+        <v>11.8</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>79.2</v>
+        <v>93.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.9</v>
+        <v>11.7</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-1.3 t/j</t>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1127,14 +1110,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>60.7</v>
+        <v>77.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.4 t/j</t>
+          <t>-1.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1150,21 +1133,21 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>57</v>
+        <v>66.5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-2.0 t/j</t>
+          <t>-0.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1173,21 +1156,21 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>50.6</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-0.1 t/j</t>
+        <v>6.9</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1196,21 +1179,21 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>44.5</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>-0.4 t/j</t>
+        <v>6.9</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1219,21 +1202,21 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>37.1</v>
+        <v>44.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>-1.2 t/j</t>
+        <v>5.6</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>+2.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1242,14 +1225,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>29.1</v>
+        <v>43.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+0.8 t/j</t>
+        <v>5.4</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1288,10 +1271,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>722.3</v>
+        <v>804</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>90.3</v>
+        <v>100.5</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1307,10 +1290,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>435.2</v>
+        <v>580.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>54.4</v>
+        <v>72.5</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1326,10 +1309,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>339.8</v>
+        <v>401</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>42.5</v>
+        <v>50.1</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1341,14 +1324,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>1511.3</v>
+        <v>1799.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>188.9</v>
+        <v>224.9</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-91.3 t/j vs 280.2</t>
+          <t>-55.3 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1345,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 188.9 t/j (3778 sacs) sur 8j.</t>
+          <t>Moyenne/jour globale: 224.9 t/j (4497 sacs) sur 8j.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1399,7 +1382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 11/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 13/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1459,41 +1442,41 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>+6 cmdes</t>
+          <t>3.9:1</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
@@ -1503,16 +1486,16 @@
           <t>2.9:1</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>-10 cmdes</t>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1521,137 +1504,137 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>1.3:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-9 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>+2 cmdes</t>
+          <t>2.8:1</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.1:1</t>
+          <t>1.0:1</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>-6 cmdes</t>
+          <t>-15 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -1660,45 +1643,45 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1707,22 +1690,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1.6:1</t>
+          <t>0.7:1</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
@@ -1738,291 +1721,198 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0.1:1</t>
+          <t>2.0:1</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Ahala</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>+2 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1.9:1</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>-8 cmdes</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>-67 cmdes vs 119</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Pk11</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1.8:1</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>-29 cmdes vs 119</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>72%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>3-5:1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>21%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>5-10:1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>5-10:1</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>10-20:1</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.1:1 (vs 2.6:1 le 31/07).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.4:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -2039,7 +1929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2056,7 +1946,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 11/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2010,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128843</t>
+          <t>SO2608-129253</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2501-01196 -  SCOOPS MOUNGO (MR NKENGUE VALENTIN)</t>
+          <t>CU2604-14454 -  DACOSTA POULTRY FARM (JETIMONEH OLIVER NKATOH)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2161,29 +2051,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128871</t>
+          <t>SO2608-129184</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00162 -  FOTSING PIERRE</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2202,29 +2092,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128820</t>
+          <t>SO2608-129207</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2243,17 +2133,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128834</t>
+          <t>SO2608-129244</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2262,10 +2152,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2284,22 +2174,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-128756</t>
+          <t>SO2608-129270</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -2320,74 +2210,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-128764</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 5 cmdes (1.2 t) le 13/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 6 cmdes (2.4 t) le 11/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2404,482 +2253,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
+          <t>TABLEAU 4 - Stock SOJA et date rupture</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 08/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs alloués SPC. Consommation = Vente + Production conc. Mise à jour 12/08/2026.</t>
+          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→10/08/2026 deduites du stock. Mise a jour 10/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sacs/jour (post-stock)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>t/jour</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Jours stock</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Date rupture</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Evolution date rupture</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Nb sacs</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Poids (t)</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Équivalent sacs 50kg</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Realiste</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3641</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>+7 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Sacs de 50kg (T102)</t>
+          <t>Acceleration +20%</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>80384</v>
+        <v>4370</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4019.2</v>
+        <v>218.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>80384</v>
+        <v>31</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+6 jours vs 29/08/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Sacs de 1kg (T1021)</t>
+          <t>Ralentissement -20%</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2245</v>
+        <v>2913</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.245</v>
+        <v>145.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 5kg (T1023)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.4</v>
+        <v>46</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>+8 jours vs 14/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Sacs de 25kg (T1024)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.5</v>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Parametres</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>STOCK BRUT TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>82634</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>4021.5</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>80430</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Stock initial (au 21/07)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>160 000 sacs</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>8000 t</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Moins: allocation SPC (entité soeur)</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>9200</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>460</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>9200</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Ventes post-stock 02→10/08</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>25 489 sacs</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1274.5 t</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>STOCK NET DISPONIBLE BELGOCAM</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="23" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>71230</v>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Stock restant au 10/08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>134 511 sacs</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>6725.5 t</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Jours ouvrables post-stock</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>7 j (lun-sam)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Moyenne/jour post-stock</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>3 641 sacs</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>182.1 t</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Flux</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Sacs/sem (lun-sam)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Sacs/jour</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>t/sem</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ventes août (total, info)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>35 984 sacs</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1799.2 t</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Vente directe soja</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>20117</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>3353</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1006</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Ventes août 9j (Livrée, 12/08 exclu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (min)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (moy)</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>4900</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>817</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
-        </is>
-      </c>
+          <t>Hausse prix soja</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>+2 000 XAF/sac le 23/07/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Production concentrés (max)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>883</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Besoin production</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock restant au 10/08/2026 = 134 511 sacs (6725.5 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MIN (vente + prod min)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>24617</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>4103</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>1231</v>
-      </c>
-      <c r="E20" s="24" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Baisse moy/jour post-stock (-21.1 t/j) — effet possible de la hausse de prix.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MOY (vente + prod moy)</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>25017</v>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>4170</v>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>1251</v>
-      </c>
-      <c r="E21" s="24" t="n"/>
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MAX (vente + prod max)</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>25417</v>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>4236</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>1271</v>
-      </c>
-      <c r="E22" s="24" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net disponible BELGOCAM, départ 11/08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Scénario</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Stock net (sacs éq. 50kg)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Conso (sacs/sem)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Jours restants</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>Semaines</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>Date rupture</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Min (conso min)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>71230</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>24617</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Moyen (conso moy)</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>71230</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>25017</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Max (conso max)</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>71230</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>25417</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Stock net BELGOCAM = 71230 sacs (3561 t) après exclusion 9 200 sacs SPC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 30/08/2026 (19 jours, 2.8 semaines).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 20/08/2026 (10 jours de marge).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4 500-5 300 sacs/sem).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 11/08 (9j, 12/08 matinal exclu).</t>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Seules les ventes 02→10/08 (post-stock) sont deduites du stock pour calculer le stock restant au 10/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 22/09/2026 (37 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -2972,18 +2630,18 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>150.3</v>
+        <v>157.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.78:1</t>
+          <t>2.73:1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="6">
@@ -3056,18 +2714,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>151.3</v>
+        <v>160</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>60.5</v>
+        <v>63.1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.54:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="9">
@@ -3085,18 +2743,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>174.7</v>
+        <v>179.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>65.2</v>
+        <v>66.8</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.68:1</t>
+          <t>2.69:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="10">
@@ -3143,18 +2801,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>144.3</v>
+        <v>155.8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>54.1</v>
+        <v>57.7</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.67:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -3172,18 +2830,18 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>38.8</v>
+        <v>39.6</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.52:1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="13">
@@ -3227,18 +2885,18 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>252.8</v>
+        <v>267.8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>101.7</v>
+        <v>110.2</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.49:1</t>
+          <t>2.43:1</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="18">

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,8 +101,14 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +140,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -161,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +193,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -260,7 +279,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -417,7 +435,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2253,291 +2270,482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture</t>
+          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 01/08/2026→10/08/2026 deduites du stock. Mise a jour 10/08/2026.</t>
+          <t>Stock physique au 08/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 14/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Sacs/jour (post-stock)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>t/jour</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Jours stock</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Date rupture</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Evolution date rupture</t>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Realiste</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>3641</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>+7 jours vs 04/09/2026</t>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Nb sacs</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Poids (t)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Équivalent sacs 50kg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Acceleration +20%</t>
+          <t>Sacs de 50kg (T102)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4370</v>
+        <v>80384</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>218.5</v>
+        <v>4019.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>+6 jours vs 29/08/2026</t>
-        </is>
+        <v>80384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ralentissement -20%</t>
+          <t>Sacs de 1kg (T1021)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2913</v>
+        <v>2245</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>145.7</v>
+        <v>2.245</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>+8 jours vs 14/09/2026</t>
-        </is>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 5kg (T1023)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Parametres</t>
-        </is>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sacs de 25kg (T1024)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Stock initial (au 21/07)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>160 000 sacs</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>8000 t</t>
-        </is>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>STOCK BRUT TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>82634</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>4021.5</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>80430</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Ventes post-stock 02→10/08</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>25 489 sacs</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>1274.5 t</t>
-        </is>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Moins: allocation SPC (entité soeur)</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>460</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>9200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Stock restant au 10/08</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>134 511 sacs</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>6725.5 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Jours ouvrables post-stock</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>7 j (lun-sam)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>STOCK NET DISPONIBLE BELGOCAM</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="23" t="n">
+        <v>3561.5</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>71230</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Moyenne/jour post-stock</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>3 641 sacs</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>182.1 t</t>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Ventes août (total, info)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>35 984 sacs</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>1799.2 t</t>
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Sacs/sem (lun-sam)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Sacs/jour</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>t/sem</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Hausse prix soja</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>+2 000 XAF/sac le 23/07/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
+          <t>Vente directe soja</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>19573</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3262</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>979</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Ventes août 11j (Livrée, 14/08 exclu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (min)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (moy)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>4900</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>817</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Stock restant au 10/08/2026 = 134 511 sacs (6725.5 t).</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Production concentrés (max)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>883</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Besoin production</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Baisse moy/jour post-stock (-21.1 t/j) — effet possible de la hausse de prix.</t>
-        </is>
-      </c>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MIN (vente + prod min)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>24073</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>4012</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MOY (vente + prod moy)</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>24473</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>4079</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Seules les ventes 02→10/08 (post-stock) sont deduites du stock pour calculer le stock restant au 10/08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 22/09/2026 (37 jours de stock restant).</t>
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL MAX (vente + prod max)</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>24873</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>4145</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1244</v>
+      </c>
+      <c r="E22" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 13/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Scénario</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Stock net (sacs éq. 50kg)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Conso (sacs/sem)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Jours restants</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Semaines</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Date rupture</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Min (conso min)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>24073</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Moyen (conso moy)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>24473</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Max (conso max)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>71230</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>24873</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock net BELGOCAM = 71230 sacs (3561 t) après exclusion 9 200 sacs SPC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 02/09/2026 (20 jours, 2.9 semaines).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 23/08/2026 (10 jours de marge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4 500-5 300 sacs/sem).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 13/08 (11j, 14/08 matinal exclu).</t>
         </is>
       </c>
     </row>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -91,6 +91,12 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
@@ -100,12 +106,6 @@
     </font>
     <font>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="8">
@@ -137,12 +137,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -190,17 +190,17 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,6 +279,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -435,6 +436,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2284,41 +2286,41 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode corrigée avec production concentrés)</t>
+          <t>TABLEAU 4 - Stock SOJA et date rupture (méthode BEKOKO + SPC + production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 08/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 14/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 13/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>1. STOCK PHYSIQUE AU 08/08/2026 (magasins centraux BEKOKO)</t>
+          <t>1. STOCK PHYSIQUE AU 01/08/2026 (magasins centraux BEKOKO)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Nb sacs</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Poids (t)</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Équivalent sacs 50kg</t>
         </is>
@@ -2389,48 +2391,44 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>STOCK BRUT TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>82634</v>
-      </c>
-      <c r="C10" s="19" t="n">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="16" t="n">
         <v>4021.5</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="16" t="n">
         <v>80430</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Moins: allocation SPC (entité soeur)</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="18" t="n">
+        <v>460</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <v>9200</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <v>460</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>9200</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>STOCK NET DISPONIBLE BELGOCAM</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="23" t="n">
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="21" t="n">
         <v>3561.5</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="21" t="n">
         <v>71230</v>
       </c>
     </row>
@@ -2442,27 +2440,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Flux</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Sacs/sem (lun-sam)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Sacs/jour</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>t/sem</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2485,7 +2483,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 11j (Livrée, 14/08 exclu)</t>
+          <t>Ventes août 11j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2553,90 +2551,90 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MIN (vente + prod min)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL MIN</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
         <v>24073</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="16" t="n">
         <v>4012</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="16" t="n">
         <v>1204</v>
       </c>
-      <c r="E20" s="24" t="n"/>
+      <c r="E20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MOY (vente + prod moy)</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL MOY</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
         <v>24473</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="16" t="n">
         <v>4079</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="16" t="n">
         <v>1224</v>
       </c>
-      <c r="E21" s="24" t="n"/>
+      <c r="E21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL MAX (vente + prod max)</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
         <v>24873</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="16" t="n">
         <v>4145</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="16" t="n">
         <v>1244</v>
       </c>
-      <c r="E22" s="24" t="n"/>
+      <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 13/08)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 13/08/2026)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Stock net (sacs éq. 50kg)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Conso (sacs/sem)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Jours restants</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Semaines</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>Date rupture</t>
         </is>
@@ -2645,7 +2643,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Min (conso min)</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
@@ -2660,7 +2658,7 @@
       <c r="E26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
@@ -2669,7 +2667,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Moyen (conso moy)</t>
+          <t>Moyen</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
@@ -2684,7 +2682,7 @@
       <c r="E27" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
@@ -2693,7 +2691,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Max (conso max)</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
@@ -2708,7 +2706,7 @@
       <c r="E28" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
@@ -2722,14 +2720,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Date de rupture probable: 02/09/2026 (20 jours, 2.9 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>URGENCE: réapprovisionnement à prévoir avant le 23/08/2026 (10 jours de marge).</t>
         </is>
@@ -2738,14 +2736,14 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4 500-5 300 sacs/sem).</t>
+          <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4500-5300 sacs/sem).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 13/08 (11j, 14/08 matinal exclu).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 13/08/2026 (11j).</t>
         </is>
       </c>
     </row>
@@ -2853,26 +2851,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3053,26 +3051,26 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3115,35 +3113,35 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$14</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$14</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$14</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$14</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$17</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$14</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$14</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$17</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 10/08/2026 (8j). Livree. lun-sam. Mise a jour 10/08/2026.</t>
+          <t>01/07 au 13/08/2026 (11j). Livree. lun-sam. Mise a jour 13/08/2026.</t>
         </is>
       </c>
     </row>
@@ -948,11 +948,11 @@
         <v>429.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>53.7</v>
+        <v>39.1</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-19.8 t/j</t>
+          <t>-34.4 t/j</t>
         </is>
       </c>
     </row>
@@ -971,11 +971,11 @@
         <v>243.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>30.4</v>
+        <v>22.1</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-1.3 t/j</t>
+          <t>-9.6 t/j</t>
         </is>
       </c>
     </row>
@@ -994,11 +994,11 @@
         <v>222.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>+5.3 t/j</t>
+        <v>20.2</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-2.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1017,11 +1017,11 @@
         <v>130.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>+0.1 t/j</t>
+        <v>11.9</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-4.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1040,11 +1040,11 @@
         <v>120.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-42.9 t/j</t>
+          <t>-47.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1063,11 +1063,11 @@
         <v>109</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.6</v>
+        <v>9.9</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>-3.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1086,11 +1086,11 @@
         <v>94.40000000000001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+0.5 t/j</t>
+        <v>8.6</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-2.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1109,11 +1109,11 @@
         <v>93.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>11.7</v>
+        <v>8.5</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1132,11 +1132,11 @@
         <v>77.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-1.4 t/j</t>
+          <t>-4.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1155,11 +1155,11 @@
         <v>66.5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.8 t/j</t>
+          <t>-3.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1178,11 +1178,11 @@
         <v>55</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>+0.9 t/j</t>
+        <v>5</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1201,11 +1201,11 @@
         <v>55</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>+0.5 t/j</t>
+        <v>5</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-1.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1224,11 +1224,11 @@
         <v>44.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>+2.7 t/j</t>
+          <t>+1.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1247,11 +1247,11 @@
         <v>43.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>-1.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>804</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>100.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1312,7 +1312,7 @@
         <v>580.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>72.5</v>
+        <v>52.7</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1331,7 +1331,7 @@
         <v>401</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>50.1</v>
+        <v>36.5</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1346,11 +1346,11 @@
         <v>1799.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>224.9</v>
+        <v>163.6</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-55.3 t/j vs 280.2</t>
+          <t>-116.7 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 224.9 t/j (4497 sacs) sur 8j.</t>
+          <t>Moyenne/jour globale: 163.6 t/j (3271 sacs) sur 11j.</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 10/08/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 13/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2780,7 +2780,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 10/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 13/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3105,43 +3105,130 @@
         <v>2.43</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2.48:1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>142.4</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>2.25:1</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2.07:1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 13-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 13-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 14-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 14-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$17</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$17</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$17</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$17</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$17</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$17</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 13/08/2026 (11j). Livree. lun-sam. Mise a jour 13/08/2026.</t>
+          <t>01/08 au 14/08/2026 (12j). Livree. lun-sam. Mise a jour 15/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,14 +945,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>429.9</v>
+        <v>431.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>39.1</v>
+        <v>35.9</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-34.4 t/j</t>
+          <t>-37.6 t/j</t>
         </is>
       </c>
     </row>
@@ -968,14 +968,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>243.3</v>
+        <v>249.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>22.1</v>
+        <v>20.8</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-9.6 t/j</t>
+          <t>-10.9 t/j</t>
         </is>
       </c>
     </row>
@@ -991,60 +991,60 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>222.5</v>
+        <v>234.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20.2</v>
+        <v>19.5</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-2.3 t/j</t>
+          <t>-3.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>130.8</v>
+        <v>146.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-4.4 t/j</t>
+          <t>-45.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>120.3</v>
+        <v>133.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-47.0 t/j</t>
+          <t>-5.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>109</v>
+        <v>123.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-3.9 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1083,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>101.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.7 t/j</t>
+          <t>-2.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1106,14 +1106,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>93.5</v>
+        <v>95</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-3.6 t/j</t>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1129,67 +1129,67 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>77.2</v>
+        <v>81.3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-4.0 t/j</t>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>66.5</v>
+        <v>72.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-3.1 t/j</t>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>55</v>
+        <v>68.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.9 t/j</t>
+          <t>-3.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>55</v>
+        <v>61.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-1.4 t/j</t>
+          <t>-0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>44.6</v>
+        <v>48.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
@@ -1247,11 +1247,11 @@
         <v>43.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-1.9 t/j</t>
+          <t>-2.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>804</v>
+        <v>814.5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>73.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>580.2</v>
+        <v>619</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>52.7</v>
+        <v>51.6</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>401</v>
+        <v>457</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>36.5</v>
+        <v>38.1</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>1799.2</v>
+        <v>1904.5</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>163.6</v>
+        <v>158.7</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-116.7 t/j vs 280.2</t>
+          <t>-121.5 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 163.6 t/j (3271 sacs) sur 11j.</t>
+          <t>Moyenne/jour globale: 158.7 t/j (3174 sacs) sur 12j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 13/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 14/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1461,29 +1461,29 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3.9:1</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1495,50 +1495,50 @@
         <v>8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>3.3:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>+7 cmdes</t>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1554,177 +1554,177 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.3:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>-9 cmdes</t>
+          <t>-10 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.0:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>-15 cmdes</t>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
+          <t>1.1:1</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>-16 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>1.3:1</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>-8 cmdes</t>
+          <t>-9 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0.7:1</t>
+          <t>2.3:1</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>-7 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1743,14 +1743,14 @@
         <v>2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.3:1</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1771,167 +1771,198 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
+          <t>0.0:1</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Mbouda</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>0.8:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-9 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>-67 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>1.8:1</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>-61 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>72%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>88%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.1:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 1.8:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1948,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1965,7 +1996,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 13/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2060,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129253</t>
+          <t>SO2608-129408</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2604-14454 -  DACOSTA POULTRY FARM (JETIMONEH OLIVER NKATOH)</t>
+          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2070,29 +2101,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129184</t>
+          <t>SO2608-129417</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>ZOCL00017 -  MME PONGANG HELENE (SOLDE COMPTA)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2111,29 +2142,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129207</t>
+          <t>SO2608-129501</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-00159 -  SIGNE WILLIAM</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2152,22 +2183,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129244</t>
+          <t>SO2608-129373</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -2193,22 +2224,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129270</t>
+          <t>SO2608-129376</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -2229,33 +2260,115 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-129392</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Djeleng</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-129439</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Messassi</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 5 cmdes (1.2 t) le 13/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 7 cmdes (3.2 t) le 14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2293,7 +2406,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 13/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 14/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2473,17 +2586,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>19573</v>
+        <v>18992</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3262</v>
+        <v>3165</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 11j (Livrée)</t>
+          <t>Ventes août 12j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2557,13 +2670,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>24073</v>
+        <v>23492</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>4012</v>
+        <v>3915</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1204</v>
+        <v>1175</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2574,13 +2687,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>24473</v>
+        <v>23892</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>4079</v>
+        <v>3982</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1224</v>
+        <v>1195</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2591,20 +2704,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>24873</v>
+        <v>24292</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4145</v>
+        <v>4049</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1244</v>
+        <v>1215</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 13/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 14/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2763,7 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>24073</v>
+        <v>23492</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>21</v>
@@ -2660,7 +2773,7 @@
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2674,17 +2787,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24473</v>
+        <v>23892</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2698,17 +2811,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>24873</v>
+        <v>24292</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2722,14 +2835,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 02/09/2026 (20 jours, 2.9 semaines).</t>
+          <t>Date de rupture probable: 03/09/2026 (20 jours, 3.0 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 23/08/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 24/08/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2856,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 13/08/2026 (11j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 14/08/2026 (12j).</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2780,7 +2893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 13/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 14/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2891,10 +3004,10 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>288.7</v>
+        <v>292.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>104.4</v>
+        <v>105.6</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -2978,18 +3091,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>122.5</v>
+        <v>125.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>54.6</v>
+        <v>55.8</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.24:1</t>
+          <t>2.25:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="11">
@@ -3149,18 +3262,18 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>142.4</v>
+        <v>149.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>63.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.25:1</t>
+          <t>2.27:1</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="17">
@@ -3178,57 +3291,86 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>48.9</v>
+        <v>65</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>23.6</v>
+        <v>29.5</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.07:1</t>
+          <t>2.21:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1.85:1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 14-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 14-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 15-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 15-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$18</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$18</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$18</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$18</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$19</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$18</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$18</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$19</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 14/08/2026 (12j). Livree. lun-sam. Mise a jour 15/08/2026.</t>
+          <t>01/08 au 15/08/2026 (13j). Livree. lun-sam. Mise a jour 16/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,60 +945,60 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>431.2</v>
+        <v>431.6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35.9</v>
+        <v>33.2</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-37.6 t/j</t>
+          <t>-40.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>249.8</v>
+        <v>258.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-10.9 t/j</t>
+          <t>-2.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>234.2</v>
+        <v>249.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-3.0 t/j</t>
+          <t>-12.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1014,14 +1014,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>146.8</v>
+        <v>164.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-45.7 t/j</t>
+          <t>-45.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1040,11 +1040,11 @@
         <v>133.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-5.2 t/j</t>
+          <t>-6.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>123.5</v>
+        <v>124.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-3.5 t/j</t>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1083,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>101.4</v>
+        <v>106</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.8 t/j</t>
+          <t>-3.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1106,14 +1106,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.2 t/j</t>
+          <t>-4.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1129,14 +1129,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>81.3</v>
+        <v>90.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-4.2 t/j</t>
+          <t>-4.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1152,67 +1152,67 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>68.5</v>
+        <v>74.5</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-3.4 t/j</t>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>61.2</v>
+        <v>73.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-0.8 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>48.1</v>
+        <v>51.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>+1.2 t/j</t>
+        <v>3.9</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-1.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1244,14 +1244,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>43.2</v>
+        <v>49.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>-2.2 t/j</t>
+        <v>3.8</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>814.5</v>
+        <v>814.8</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>67.90000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>619</v>
+        <v>663.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>457</v>
+        <v>503.9</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>1904.5</v>
+        <v>1995.9</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>158.7</v>
+        <v>153.5</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-121.5 t/j vs 280.2</t>
+          <t>-126.7 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 158.7 t/j (3174 sacs) sur 12j.</t>
+          <t>Moyenne/jour globale: 153.5 t/j (3070 sacs) sur 13j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 14/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 15/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1452,22 +1452,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>+7 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1523,20 +1523,20 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3.3:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>+2 cmdes</t>
         </is>
@@ -1545,31 +1545,31 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>-10 cmdes</t>
+          <t>5.7:1</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1595,10 +1595,10 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+          <t>0.3:1</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>-2 cmdes</t>
         </is>
@@ -1607,31 +1607,31 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1647,29 +1647,29 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1.1:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-16 cmdes</t>
+          <t>0.5:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>-17 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1678,84 +1678,84 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1.3:1</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-9 cmdes</t>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>-12 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>-9 cmdes</t>
         </is>
       </c>
     </row>
@@ -1781,146 +1781,130 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0.0:1</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Mbouda</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>0.8:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>-9 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>1.8:1</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>-61 cmdes vs 119</t>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>-70 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
@@ -1932,37 +1916,22 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 1.8:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.4:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1979,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1996,7 +1965,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 14/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 15/08/2026</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2029,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129408</t>
+          <t>SO2608-129579</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
+          <t>CU2408-01052 -  Chedjou André (CHENJOU ANDRE)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2079,10 +2048,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2101,12 +2070,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129417</t>
+          <t>SO2608-129527</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>ZOCL00017 -  MME PONGANG HELENE (SOLDE COMPTA)</t>
+          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2142,12 +2111,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129501</t>
+          <t>SO2608-129591</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00159 -  SIGNE WILLIAM</t>
+          <t>CU2407-00168 -  KAMGNO PIERRE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2183,29 +2152,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129373</t>
+          <t>SO2608-129636</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2224,29 +2193,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129376</t>
+          <t>SO2608-129546</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2265,22 +2234,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129392</t>
+          <t>SO2608-129623</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2508-13571 -  TALLA TESSO MEFENYA TIBEAU</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -2301,74 +2270,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-129439</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Messassi</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 6 cmdes (3.8 t) le 15/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 7 cmdes (3.2 t) le 14/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2406,7 +2334,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 14/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 15/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2586,17 +2514,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18992</v>
+        <v>18424</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3165</v>
+        <v>3071</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>950</v>
+        <v>921</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 12j (Livrée)</t>
+          <t>Ventes août 13j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2670,13 +2598,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>23492</v>
+        <v>22924</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3915</v>
+        <v>3821</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1175</v>
+        <v>1146</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2687,13 +2615,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>23892</v>
+        <v>23324</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3982</v>
+        <v>3887</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1195</v>
+        <v>1166</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2704,20 +2632,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>24292</v>
+        <v>23724</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4049</v>
+        <v>3954</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1215</v>
+        <v>1186</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 14/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 15/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2763,17 +2691,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>23492</v>
+        <v>22924</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2715,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>23892</v>
+        <v>23324</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2811,17 +2739,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>24292</v>
+        <v>23724</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2835,14 +2763,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 03/09/2026 (20 jours, 3.0 semaines).</t>
+          <t>Date de rupture probable: 05/09/2026 (21 jours, 3.1 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 24/08/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 26/08/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2784,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 14/08/2026 (12j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 15/08/2026 (13j).</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2893,7 +2821,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 14/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 15/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2949,18 +2877,18 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>157.3</v>
+        <v>167.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>57.6</v>
+        <v>60.6</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.73:1</t>
+          <t>2.76:1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="6">
@@ -3233,18 +3161,18 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>171.1</v>
+        <v>175.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.48:1</t>
+          <t>2.49:1</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="16">
@@ -3291,18 +3219,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>65</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>29.5</v>
+        <v>34.5</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.21:1</t>
+          <t>2.16:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="18">
@@ -3320,57 +3248,86 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>74.8</v>
+        <v>102.5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>40.5</v>
+        <v>51.1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1.85:1</t>
+          <t>2.01:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>2.43:1</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 15-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 15-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 17-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 17-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$19</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$19</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$19</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$19</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$21</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$19</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$19</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 15/08/2026 (13j). Livree. lun-sam. Mise a jour 16/08/2026.</t>
+          <t>01/08 au 17/08/2026 (14j). Livree. lun-sam. Mise a jour 18/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,14 +945,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>431.6</v>
+        <v>443</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>33.2</v>
+        <v>31.6</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-40.3 t/j</t>
+          <t>-41.9 t/j</t>
         </is>
       </c>
     </row>
@@ -968,14 +968,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>258.6</v>
+        <v>281.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-2.7 t/j</t>
+          <t>-2.5 t/j</t>
         </is>
       </c>
     </row>
@@ -991,14 +991,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>249.8</v>
+        <v>254.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-12.5 t/j</t>
+          <t>-13.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1014,14 +1014,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>164.4</v>
+        <v>225.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.6</v>
+        <v>16.1</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-45.3 t/j</t>
+          <t>-41.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>133.4</v>
+        <v>133.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-6.0 t/j</t>
+          <t>-6.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>124.8</v>
+        <v>125</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4.2 t/j</t>
+          <t>-4.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>106</v>
+        <v>114.1</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>8.199999999999999</v>
@@ -1106,14 +1106,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>98</v>
+        <v>103.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.6 t/j</t>
+          <t>-4.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1129,14 +1129,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>90.8</v>
+        <v>96.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-4.0 t/j</t>
+          <t>-4.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1152,14 +1152,14 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>76.2</v>
+        <v>96.2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>-0.5 t/j</t>
+        <v>6.9</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1178,11 +1178,11 @@
         <v>74.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>-0.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1201,18 +1201,18 @@
         <v>73.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-3.5 t/j</t>
+          <t>-3.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>51.2</v>
+        <v>61</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>-1.9 t/j</t>
+        <v>4.4</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>+1.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1244,14 +1244,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>49.2</v>
+        <v>51.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+0.9 t/j</t>
+        <v>3.7</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-2.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>814.8</v>
+        <v>831.5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>62.7</v>
+        <v>59.4</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>663.2</v>
+        <v>705.8</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>503.9</v>
+        <v>596.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>38.8</v>
+        <v>42.6</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>1995.9</v>
+        <v>2147.4</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>153.5</v>
+        <v>153.4</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-126.7 t/j vs 280.2</t>
+          <t>-126.8 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 153.5 t/j (3070 sacs) sur 13j.</t>
+          <t>Moyenne/jour globale: 153.4 t/j (3067 sacs) sur 14j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 15/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 17/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1452,38 +1452,38 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1492,60 +1492,60 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>+5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>1.9:1</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>5.7:1</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
@@ -1585,146 +1585,146 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>0.3:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>0.5:1</t>
+          <t>2.3:1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>-17 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>0.7:1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-18 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0.4:1</t>
+          <t>0.3:1</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>-12 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
@@ -1743,153 +1743,137 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
+          <t>0.2:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>-9 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1.2:1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>-8 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>-70 cmdes vs 119</t>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>1.8:1</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>-47 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
@@ -1901,37 +1885,22 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.4:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 1.8:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1948,7 +1917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1965,7 +1934,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 15/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,12 +1998,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129579</t>
+          <t>SO2608-129819</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2408-01052 -  Chedjou André (CHENJOU ANDRE)</t>
+          <t>CU2407-00171 -  MME NGOBOU SOREL</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2048,10 +2017,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2070,12 +2039,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129527</t>
+          <t>SO2608-129844</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
+          <t>ZOCL00002000 -  KUHLIFARM COOP-BOD (KUHLIFARM COOP-BOD)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2111,29 +2080,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129591</t>
+          <t>SO2608-129668</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00168 -  KAMGNO PIERRE</t>
+          <t>CU2408-01068 -  CLIENT COMPTOIR MBOUDA (CLIENT COMPTOIR)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2152,29 +2121,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129636</t>
+          <t>SO2608-129813</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2193,29 +2162,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129546</t>
+          <t>SO2608-129684</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2234,17 +2203,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129623</t>
+          <t>SO2608-129795</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2508-13571 -  TALLA TESSO MEFENYA TIBEAU</t>
+          <t>CU2407-00138 -  CLIENTS COMPTOIR AHALA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2270,33 +2239,74 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-129784</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Nkolbisson</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 6 cmdes (3.8 t) le 15/08/2026</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 7 cmdes (3.6 t) le 17/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2334,7 +2344,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 15/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 17/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2514,17 +2524,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18424</v>
+        <v>18395</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3071</v>
+        <v>3066</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 13j (Livrée)</t>
+          <t>Ventes août 14j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2598,13 +2608,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>22924</v>
+        <v>22895</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3821</v>
+        <v>3816</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2615,13 +2625,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>23324</v>
+        <v>23295</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3887</v>
+        <v>3882</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2632,20 +2642,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>23724</v>
+        <v>23695</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>3954</v>
+        <v>3949</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 15/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 17/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2701,7 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>22924</v>
+        <v>22895</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>22</v>
@@ -2701,7 +2711,7 @@
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2725,7 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>23324</v>
+        <v>23295</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>21</v>
@@ -2725,7 +2735,7 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2749,7 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23724</v>
+        <v>23695</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21</v>
@@ -2749,7 +2759,7 @@
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2763,14 +2773,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 05/09/2026 (21 jours, 3.1 semaines).</t>
+          <t>Date de rupture probable: 07/09/2026 (21 jours, 3.1 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 26/08/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 28/08/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2794,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 15/08/2026 (13j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 17/08/2026 (14j).</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2821,7 +2831,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 15/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 17/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2877,18 +2887,18 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>167.3</v>
+        <v>174.8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>60.6</v>
+        <v>63.1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.76:1</t>
+          <t>2.77:1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
@@ -2961,10 +2971,10 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>160</v>
+        <v>161.1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>63.1</v>
+        <v>63.5</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -2990,18 +3000,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>179.7</v>
+        <v>182.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66.8</v>
+        <v>67.8</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.69:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -3019,18 +3029,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>125.7</v>
+        <v>127.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>55.8</v>
+        <v>56.7</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.25:1</t>
+          <t>2.26:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="11">
@@ -3048,18 +3058,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>155.8</v>
+        <v>180.8</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>57.7</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>3.13:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12">
@@ -3132,18 +3142,18 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>267.8</v>
+        <v>281.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>110.2</v>
+        <v>114.6</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.43:1</t>
+          <t>2.46:1</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="15">
@@ -3161,18 +3171,18 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>175.8</v>
+        <v>184.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.49:1</t>
+          <t>2.52:1</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="16">
@@ -3190,10 +3200,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>149.4</v>
+        <v>149.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -3219,18 +3229,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.16:1</t>
+          <t>2.15:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="18">
@@ -3248,18 +3258,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>102.5</v>
+        <v>106</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>51.1</v>
+        <v>52.5</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2.01:1</t>
+          <t>2.02:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="19">
@@ -3277,57 +3287,112 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>44.8</v>
+        <v>50.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>18.4</v>
+        <v>21.7</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2.43:1</t>
+          <t>2.34:1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1.83:1</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 17-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 17-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 19-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 19-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$21</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$21</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$21</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$21</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$23</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$21</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$21</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 17/08/2026 (14j). Livree. lun-sam. Mise a jour 18/08/2026.</t>
+          <t>01/08 au 19/08/2026 (16j). Livree. lun-sam. Mise a jour 20/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,37 +945,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>443</v>
+        <v>622.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>31.6</v>
+        <v>38.9</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-41.9 t/j</t>
+          <t>-34.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>281.1</v>
+        <v>356.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.1</v>
+        <v>22.3</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-2.5 t/j</t>
+          <t>-35.7 t/j</t>
         </is>
       </c>
     </row>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>254.8</v>
+        <v>351.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>18.2</v>
+        <v>22</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-13.5 t/j</t>
+          <t>-9.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>225.5</v>
+        <v>328.3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16.1</v>
+        <v>20.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-41.8 t/j</t>
+          <t>-2.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>133.7</v>
+        <v>185.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-6.7 t/j</t>
+          <t>-4.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>125</v>
+        <v>154.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4.8 t/j</t>
+          <t>-4.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1083,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>114.1</v>
+        <v>136.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-3.1 t/j</t>
+          <t>-2.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>103.5</v>
+        <v>131.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.7 t/j</t>
+          <t>-3.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>96.5</v>
+        <v>117.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>-4.1 t/j</t>
+        <v>7.3</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+1.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1152,14 +1152,14 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>96.2</v>
+        <v>109.9</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+0.5 t/j</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1175,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>74.5</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.6 t/j</t>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1198,21 +1198,21 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>73.3</v>
+        <v>90.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-3.9 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>61</v>
+        <v>75.7</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>+1.5 t/j</t>
+        <v>4.7</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-1.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1244,14 +1244,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>51.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>-2.1 t/j</t>
+        <v>4.1</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+1.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>831.5</v>
+        <v>1159.3</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>59.4</v>
+        <v>72.5</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>705.8</v>
+        <v>851.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>50.4</v>
+        <v>53.2</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>596.2</v>
+        <v>808.8</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>42.6</v>
+        <v>50.5</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>2147.4</v>
+        <v>2833.3</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>153.4</v>
+        <v>177.1</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-126.8 t/j vs 280.2</t>
+          <t>-103.1 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 153.4 t/j (3067 sacs) sur 14j.</t>
+          <t>Moyenne/jour globale: 177.1 t/j (3541 sacs) sur 16j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 17/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 19/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1452,62 +1452,62 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>+17 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>+5 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>+3 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
@@ -1585,153 +1585,153 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>1.4:1</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>+6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>0.7:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>0.7:1</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-18 cmdes</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0.3:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1740,167 +1740,260 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>0.1:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-17 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Nkolbisson</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ndobo</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-10 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Buea</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>0.2:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-9 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>1.8:1</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>-47 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>-22 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3-5:1</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>5-10:1</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>85%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>3-5:1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>5-10:1</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="B26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 1.8:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.0:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1917,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1934,7 +2027,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 17/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1998,12 +2091,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129819</t>
+          <t>SO2608-130302</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00171 -  MME NGOBOU SOREL</t>
+          <t>CU2407-00337 -  STE FERME AVICOLE DE L'ESPERENCE ENYOKI NKONGSAMBA-SARL (FAEE)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2017,10 +2110,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2039,12 +2132,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129844</t>
+          <t>SO2608-130314</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>ZOCL00002000 -  KUHLIFARM COOP-BOD (KUHLIFARM COOP-BOD)</t>
+          <t>CU2407-00163 -  MME DJALEU TCHAGOUE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2080,29 +2173,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129668</t>
+          <t>SO2608-130316</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2408-01068 -  CLIENT COMPTOIR MBOUDA (CLIENT COMPTOIR)</t>
+          <t>CU2607-14576 -  KINGDOM FARM ENTREPRISE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2121,7 +2214,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-129813</t>
+          <t>SO2608-130288</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2140,10 +2233,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2157,156 +2250,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-129684</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Pk11</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-129795</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00138 -  CLIENTS COMPTOIR AHALA</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Ahala</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-129784</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Nkolbisson</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 4 cmdes (3.5 t) le 19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 7 cmdes (3.6 t) le 17/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2344,7 +2314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 17/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 19/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2524,17 +2494,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18395</v>
+        <v>20974</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3066</v>
+        <v>3496</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>920</v>
+        <v>1049</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 14j (Livrée)</t>
+          <t>Ventes août 16j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2608,13 +2578,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>22895</v>
+        <v>25474</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3816</v>
+        <v>4246</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1145</v>
+        <v>1274</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2625,13 +2595,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>23295</v>
+        <v>25874</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3882</v>
+        <v>4312</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1165</v>
+        <v>1294</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2642,20 +2612,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>23695</v>
+        <v>26274</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>3949</v>
+        <v>4379</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1185</v>
+        <v>1314</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 17/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 19/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2701,13 +2671,13 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>22895</v>
+        <v>25474</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
@@ -2725,13 +2695,13 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>23295</v>
+        <v>25874</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
@@ -2749,17 +2719,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23695</v>
+        <v>26274</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2743,7 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 07/09/2026 (21 jours, 3.1 semaines).</t>
+          <t>Date de rupture probable: 07/09/2026 (19 jours, 2.8 semaines).</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2764,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 17/08/2026 (14j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 19/08/2026 (16j).</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2831,7 +2801,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 17/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 19/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2887,18 +2857,18 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>174.8</v>
+        <v>190.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>63.1</v>
+        <v>68.5</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.77:1</t>
+          <t>2.78:1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -2942,18 +2912,18 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>292.7</v>
+        <v>297.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>105.6</v>
+        <v>106.3</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.77:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -2971,18 +2941,18 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>161.1</v>
+        <v>184.6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>63.5</v>
+        <v>71.7</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.54:1</t>
+          <t>2.57:1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="9">
@@ -3000,18 +2970,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>182.7</v>
+        <v>196.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>67.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>2.78:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="10">
@@ -3029,18 +2999,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>127.9</v>
+        <v>141.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>56.7</v>
+        <v>61.4</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.26:1</t>
+          <t>2.31:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="11">
@@ -3058,18 +3028,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>180.8</v>
+        <v>188.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>57.7</v>
+        <v>59.9</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.13:1</t>
+          <t>3.15:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="12">
@@ -3087,18 +3057,18 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>109.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>39.6</v>
+        <v>42.5</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.52:1</t>
+          <t>2.57:1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="13">
@@ -3142,10 +3112,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>281.4</v>
+        <v>296.9</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>114.6</v>
+        <v>120.6</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -3171,18 +3141,18 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>184.4</v>
+        <v>206.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>73.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.52:1</t>
+          <t>2.47:1</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="16">
@@ -3200,18 +3170,18 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>149.5</v>
+        <v>160</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>66</v>
+        <v>71.2</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.27:1</t>
+          <t>2.25:1</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17">
@@ -3229,18 +3199,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>75.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>35</v>
+        <v>38.2</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.15:1</t>
+          <t>2.24:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="18">
@@ -3258,18 +3228,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>106</v>
+        <v>117.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>52.5</v>
+        <v>57.1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2.02:1</t>
+          <t>2.06:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="19">
@@ -3287,18 +3257,18 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>50.8</v>
+        <v>53.9</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2.34:1</t>
+          <t>2.44:1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="20">
@@ -3342,57 +3312,115 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>116.5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>42.9</v>
+        <v>57.8</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1.83:1</t>
+          <t>2.02:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>2.42:1</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1.98:1</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 19-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 19-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 20-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 20-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$23</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$23</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$23</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$23</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$23</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$23</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 19/08/2026 (16j). Livree. lun-sam. Mise a jour 20/08/2026.</t>
+          <t>01/08 au 20/08/2026 (17j). Livree. lun-sam. Mise a jour 21/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,14 +945,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>622.9</v>
+        <v>646.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>38.9</v>
+        <v>38</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-34.6 t/j</t>
+          <t>-35.5 t/j</t>
         </is>
       </c>
     </row>
@@ -968,14 +968,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>356.7</v>
+        <v>364.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-35.7 t/j</t>
+          <t>-36.5 t/j</t>
         </is>
       </c>
     </row>
@@ -991,14 +991,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>351.2</v>
+        <v>356.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-9.8 t/j</t>
+          <t>-10.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1014,14 +1014,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>328.3</v>
+        <v>336.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-2.0 t/j</t>
+          <t>-2.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>185.2</v>
+        <v>195.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-4.7 t/j</t>
+          <t>-4.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>154.9</v>
+        <v>161.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4.1 t/j</t>
+          <t>-4.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1083,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>136.9</v>
+        <v>146.8</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>8.6</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.7 t/j</t>
+          <t>-2.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>131.7</v>
+        <v>137</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-3.9 t/j</t>
+          <t>-4.0 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>117.5</v>
+        <v>130</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>+1.0 t/j</t>
+        <v>7.6</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-3.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1152,14 +1152,14 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>109.9</v>
+        <v>117.8</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>-4.2 t/j</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1175,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>93</v>
+        <v>100.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>-0.1 t/j</t>
+        <v>5.9</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>90.2</v>
+        <v>94.8</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-3.5 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>75.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>4.7</v>
@@ -1244,14 +1244,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+1.2 t/j</t>
+          <t>+1.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1159.3</v>
+        <v>1197.9</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>72.5</v>
+        <v>70.5</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>851.2</v>
+        <v>887.1</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>808.8</v>
+        <v>850.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>2833.3</v>
+        <v>2949.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>177.1</v>
+        <v>173.5</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-103.1 t/j vs 280.2</t>
+          <t>-106.7 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 177.1 t/j (3541 sacs) sur 16j.</t>
+          <t>Moyenne/jour globale: 173.5 t/j (3469 sacs) sur 17j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 19/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 20/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1461,44 +1461,44 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+17 cmdes</t>
+          <t>+19 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1523,103 +1523,103 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>3.4:1</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-9 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.4:1</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -1629,16 +1629,16 @@
           <t>2.3:1</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>+6 cmdes</t>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1647,60 +1647,60 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>0.7:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1709,17 +1709,17 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1731,31 +1731,31 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>0.1:1</t>
+          <t>4.5:1</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>-17 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
@@ -1774,14 +1774,14 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
+          <t>0.9:1</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1805,10 +1805,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -1817,183 +1817,214 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>-10 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
+          <t>0.1:1</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Nkongsamba</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>0.2:1</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>-22 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>-17 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>85%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>77%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.0:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.2:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -2010,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2027,7 +2058,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 19/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2091,17 +2122,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130302</t>
+          <t>SO2608-130528</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00337 -  STE FERME AVICOLE DE L'ESPERENCE ENYOKI NKONGSAMBA-SARL (FAEE)</t>
+          <t>CU2407-00459 -  PROV DES ELEVEURS KENDECK</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2110,10 +2141,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2132,22 +2163,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130314</t>
+          <t>SO2608-130431</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00163 -  MME DJALEU TCHAGOUE</t>
+          <t>CU2407-00722 -  KUE FOTSO ARNAULO</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -2173,29 +2204,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130316</t>
+          <t>SO2608-130508</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2607-14576 -  KINGDOM FARM ENTREPRISE</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2214,69 +2245,233 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130288</t>
+          <t>SO2608-130509</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130510</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130453</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Nkolbisson</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130548</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Bertoua</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130551</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 4 cmdes (3.5 t) le 19/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 8 cmdes (2.5 t) le 20/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2314,7 +2509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 19/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 20/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2494,17 +2689,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>20974</v>
+        <v>20001</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3496</v>
+        <v>3333</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1049</v>
+        <v>1000</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 16j (Livrée)</t>
+          <t>Ventes août 17j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2578,13 +2773,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>25474</v>
+        <v>24501</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>4246</v>
+        <v>4083</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1274</v>
+        <v>1225</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2595,13 +2790,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>25874</v>
+        <v>24901</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>4312</v>
+        <v>4150</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1294</v>
+        <v>1245</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2612,20 +2807,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>26274</v>
+        <v>25301</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4379</v>
+        <v>4217</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1314</v>
+        <v>1265</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 19/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 20/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2671,17 +2866,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>25474</v>
+        <v>24501</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2695,17 +2890,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>25874</v>
+        <v>24901</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2719,17 +2914,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>26274</v>
+        <v>25301</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2743,14 +2938,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 07/09/2026 (19 jours, 2.8 semaines).</t>
+          <t>Date de rupture probable: 09/09/2026 (20 jours, 2.9 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 28/08/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 30/08/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2959,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 19/08/2026 (16j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 20/08/2026 (17j).</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2801,7 +2996,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 19/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 20/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3141,10 +3336,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>206.4</v>
+        <v>207.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -3228,18 +3423,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>117.8</v>
+        <v>125.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>57.1</v>
+        <v>60.3</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2.06:1</t>
+          <t>2.09:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="19">
@@ -3312,18 +3507,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>116.5</v>
+        <v>125.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>57.8</v>
+        <v>61.8</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2.02:1</t>
+          <t>2.03:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="22">
@@ -3341,18 +3536,18 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>333.7</v>
+        <v>340.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>137.8</v>
+        <v>140.4</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2.42:1</t>
+          <t>2.43:1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="23">
@@ -3370,57 +3565,86 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>116.8</v>
+        <v>128.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>58.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>1.98:1</t>
+          <t>2.01:1</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>2.22:1</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 20-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 20-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 21-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 21-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -77,11 +77,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -325,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$24</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$24</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$24</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$24</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$24</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$24</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 20/08/2026 (17j). Livree. lun-sam. Mise a jour 21/08/2026.</t>
+          <t>01/08 au 21/08/2026 (18j). Livree. lun-sam. Mise a jour 22/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,14 +945,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>646.2</v>
+        <v>646.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>38</v>
+        <v>35.9</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-35.5 t/j</t>
+          <t>-37.6 t/j</t>
         </is>
       </c>
     </row>
@@ -968,60 +968,60 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>364.9</v>
+        <v>373.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-36.5 t/j</t>
+          <t>-37.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>356.2</v>
+        <v>367.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-10.8 t/j</t>
+          <t>-2.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>336.9</v>
+        <v>356.2</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>19.8</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-2.7 t/j</t>
+          <t>-11.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>195.4</v>
+        <v>198.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-4.8 t/j</t>
+          <t>-5.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>161.7</v>
+        <v>163.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4.3 t/j</t>
+          <t>-4.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>146.8</v>
+        <v>158.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.6 t/j</t>
+          <t>-2.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>137</v>
+        <v>142.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.0 t/j</t>
+          <t>-3.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1129,14 +1129,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>130</v>
+        <v>137.7</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>7.6</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.4 t/j</t>
+          <t>-4.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1155,11 +1155,11 @@
         <v>117.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>+0.5 t/j</t>
+          <t>+0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1175,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>100.5</v>
+        <v>104.1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>5.8</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>5.6</v>
@@ -1221,14 +1221,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-1.1 t/j</t>
+          <t>-0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>3.9</v>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1197.9</v>
+        <v>1201</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>70.5</v>
+        <v>66.7</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>887.1</v>
+        <v>948.8</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>52.2</v>
+        <v>52.7</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>850.2</v>
+        <v>875.1</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>2949.2</v>
+        <v>3038.9</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>173.5</v>
+        <v>168.8</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-106.7 t/j vs 280.2</t>
+          <t>-111.4 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 173.5 t/j (3469 sacs) sur 17j.</t>
+          <t>Moyenne/jour globale: 168.8 t/j (3376 sacs) sur 18j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 20/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 21/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1452,31 +1452,31 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+19 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1495,17 +1495,17 @@
         <v>10</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>2.4:1</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>+3 cmdes</t>
         </is>
@@ -1523,29 +1523,29 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>3.7:1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>-9 cmdes</t>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1585,34 +1585,34 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>0.5:1</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -1626,143 +1626,143 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>+4 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>4.5:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>-19 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1771,260 +1771,167 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>-58 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>3-5:1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>5-10:1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>0.9:1</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Pk11</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>0.1:1</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Nkongsamba</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>0.2:1</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n">
-        <v>102</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>-17 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>5-10:1</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>10-20:1</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.1:1 (vs 2.6:1 le 31/07).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.2:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -2041,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2058,7 +1965,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 20/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2122,17 +2029,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130528</t>
+          <t>SO2608-130625</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00459 -  PROV DES ELEVEURS KENDECK</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2141,10 +2048,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2163,29 +2070,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130431</t>
+          <t>SO2608-130610</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00722 -  KUE FOTSO ARNAULO</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2204,12 +2111,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130508</t>
+          <t>SO2608-130682</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2508-13645 -  BOASSEN OBELABOUT BIENVENU</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2223,255 +2130,50 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130509</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130510</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="G8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130453</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Nkolbisson</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 3 cmdes (0.1 t) le 21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130548</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130551</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 8 cmdes (2.5 t) le 20/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2509,7 +2211,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 20/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 21/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2689,17 +2391,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>20001</v>
+        <v>18974</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3333</v>
+        <v>3162</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1000</v>
+        <v>949</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 17j (Livrée)</t>
+          <t>Ventes août 18j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2773,13 +2475,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>24501</v>
+        <v>23474</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>4083</v>
+        <v>3912</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1225</v>
+        <v>1174</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2790,13 +2492,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>24901</v>
+        <v>23874</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>4150</v>
+        <v>3979</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1245</v>
+        <v>1194</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2807,20 +2509,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>25301</v>
+        <v>24274</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4217</v>
+        <v>4046</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1265</v>
+        <v>1214</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 20/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 21/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2866,17 +2568,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>24501</v>
+        <v>23474</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
@@ -2890,17 +2592,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24901</v>
+        <v>23874</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2914,17 +2616,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>25301</v>
+        <v>24274</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2938,14 +2640,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 09/09/2026 (20 jours, 2.9 semaines).</t>
+          <t>Date de rupture probable: 10/09/2026 (20 jours, 3.0 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 30/08/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 31/08/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2661,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 20/08/2026 (17j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 21/08/2026 (18j).</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2996,7 +2698,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 20/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 21/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3507,18 +3209,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>125.6</v>
+        <v>130.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>61.8</v>
+        <v>63.4</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2.03:1</t>
+          <t>2.06:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="22">
@@ -3536,10 +3238,10 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>340.7</v>
+        <v>341.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>140.4</v>
+        <v>140.6</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -3565,18 +3267,18 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>128.6</v>
+        <v>135.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2.01:1</t>
+          <t>2.03:1</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="24">
@@ -3594,57 +3296,86 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>104.7</v>
+        <v>136.6</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>47.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2.22:1</t>
+          <t>1.97:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2.13:1</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 21-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 21-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 22-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 22-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,10 +78,6 @@
     </font>
     <font>
       <color rgb="00008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -172,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,20 +183,19 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -325,12 +320,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$25</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$25</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +355,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$25</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$25</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$26</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +467,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$25</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$25</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -902,7 +897,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 21/08/2026 (18j). Livree. lun-sam. Mise a jour 22/08/2026.</t>
+          <t>01/08 au 22/08/2026 (19j). Livree. lun-sam. Mise a jour 23/08/2026.</t>
         </is>
       </c>
     </row>
@@ -945,60 +940,60 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>646.3</v>
+        <v>650.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35.9</v>
+        <v>34.2</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-37.6 t/j</t>
+          <t>-39.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>373.3</v>
+        <v>377.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-37.2 t/j</t>
+          <t>-2.7 t/j</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>367.8</v>
+        <v>376.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-2.1 t/j</t>
+          <t>-38.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1017,11 +1012,11 @@
         <v>356.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-11.9 t/j</t>
+          <t>-13.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1040,11 +1035,11 @@
         <v>198.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-5.3 t/j</t>
+          <t>-5.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1055,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>163.2</v>
+        <v>166.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4.7 t/j</t>
+          <t>-5.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1083,21 +1078,21 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>158.1</v>
+        <v>160.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.5 t/j</t>
+          <t>-2.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1106,21 +1101,21 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>142.3</v>
+        <v>145.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-3.1 t/j</t>
+          <t>-4.4 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1129,14 +1124,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>137.7</v>
+        <v>142.3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-4.5 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1155,11 +1150,11 @@
         <v>117.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+0.2 t/j</t>
+        <v>6.2</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1170,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>104.1</v>
+        <v>107.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1198,10 +1193,10 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>100</v>
+        <v>105.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -1221,7 +1216,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>89</v>
+        <v>93.2</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>4.9</v>
@@ -1244,7 +1239,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>70.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>3.9</v>
@@ -1270,7 +1265,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>66.7</v>
+        <v>63.4</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1309,10 +1304,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>948.8</v>
+        <v>977.4</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>52.7</v>
+        <v>51.4</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1328,10 +1323,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>875.1</v>
+        <v>889.8</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>48.6</v>
+        <v>46.8</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1343,14 +1338,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>3038.9</v>
+        <v>3086.3</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>168.8</v>
+        <v>162.4</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-111.4 t/j vs 280.2</t>
+          <t>-117.8 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1359,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 168.8 t/j (3376 sacs) sur 18j.</t>
+          <t>Moyenne/jour globale: 162.4 t/j (3248 sacs) sur 19j.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1396,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 21/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 22/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1461,91 +1456,91 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>1.9:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>+3 cmdes</t>
+          <t>0.8:1</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3.7:1</t>
+          <t>5.5:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>-11 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1554,91 +1549,91 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>+2 cmdes</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>0.5:1</t>
+          <t>2.1:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>-8 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>3.6:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1647,29 +1642,29 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1678,34 +1673,34 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>0.3:1</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -1719,24 +1714,24 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>3.2:1</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>-8 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1750,146 +1745,130 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>-19 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Nkoabang</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>-58 cmdes vs 119</t>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>-68 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
@@ -1901,37 +1880,22 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.1:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.0:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1948,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1965,7 +1929,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 21/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 22/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,29 +1993,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130625</t>
+          <t>SO2608-130859</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2407-00618 -  FOTSO BRUNO</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2070,29 +2034,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130610</t>
+          <t>SO2608-130836</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+          <t>CU2407-00289 -  LIEDJI ALAIN PIERRE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2111,69 +2075,356 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130682</t>
+          <t>SO2608-130822</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2508-13645 -  BOASSEN OBELABOUT BIENVENU</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130887</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>Ngaoundere</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="F8" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130788</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130841</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130819</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Messassi</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130846</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130852</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-130795</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Village</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 3 cmdes (0.1 t) le 21/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 10 cmdes (4.7 t) le 22/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2211,34 +2462,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 21/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 22/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>1. STOCK PHYSIQUE AU 01/08/2026 (magasins centraux BEKOKO)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Nb sacs</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Poids (t)</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Équivalent sacs 50kg</t>
         </is>
@@ -2309,76 +2560,76 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>STOCK BRUT TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="15" t="n">
         <v>4021.5</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>80430</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Moins: allocation SPC (entité soeur)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="17" t="n">
         <v>460</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>9200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>STOCK NET DISPONIBLE BELGOCAM</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="21" t="n">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="20" t="n">
         <v>3561.5</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <v>71230</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Flux</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Sacs/sem (lun-sam)</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Sacs/jour</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>t/sem</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2391,17 +2642,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18974</v>
+        <v>18042</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3162</v>
+        <v>3007</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>949</v>
+        <v>902</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 18j (Livrée)</t>
+          <t>Ventes août 19j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2469,90 +2720,90 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>TOTAL MIN</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>23474</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>3912</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>1174</v>
-      </c>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="15" t="n">
+        <v>22542</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>3757</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>1127</v>
+      </c>
+      <c r="E20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>TOTAL MOY</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>23874</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>3979</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>1194</v>
-      </c>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="15" t="n">
+        <v>22942</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>3824</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>1147</v>
+      </c>
+      <c r="E21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>TOTAL MAX</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>24274</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>4046</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>1214</v>
-      </c>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="15" t="n">
+        <v>23342</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>3890</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>1167</v>
+      </c>
+      <c r="E22" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 21/08/2026)</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 22/08/2026)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Stock net (sacs éq. 50kg)</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Conso (sacs/sem)</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Jours restants</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Semaines</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Date rupture</t>
         </is>
@@ -2568,17 +2819,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>23474</v>
+        <v>22542</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
+        <v>3.2</v>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2843,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>23874</v>
+        <v>22942</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
+        <v>3.1</v>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2867,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>24274</v>
+        <v>23342</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
+        <v>3.1</v>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>
@@ -2638,30 +2889,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 10/09/2026 (20 jours, 3.0 semaines).</t>
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 12/09/2026 (21 jours, 3.1 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 31/08/2026 (10 jours de marge).</t>
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 02/09/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4500-5300 sacs/sem).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 21/08/2026 (18j).</t>
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 22/08/2026 (19j).</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2698,7 +2949,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 21/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 22/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2769,26 +3020,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2969,26 +3220,26 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3125,10 +3376,10 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>125.8</v>
+        <v>127.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -3169,26 +3420,26 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>16/08/2026</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3209,18 +3460,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>130.6</v>
+        <v>135</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>63.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2.06:1</t>
+          <t>2.08:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="22">
@@ -3238,18 +3489,18 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>341.7</v>
+        <v>342.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>140.6</v>
+        <v>141.6</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2.43:1</t>
+          <t>2.42:1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="23">
@@ -3267,10 +3518,10 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>135.3</v>
+        <v>138.9</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -3296,18 +3547,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>136.6</v>
+        <v>137.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>1.97:1</t>
+          <t>1.98:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="25">
@@ -3325,57 +3576,86 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>56</v>
+        <v>59.9</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>26.2</v>
+        <v>27.9</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2.13:1</t>
+          <t>2.15:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>2.01:1</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 22-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 22-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 25-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 25-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
@@ -101,10 +105,14 @@
       <color rgb="00808080"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -141,6 +149,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -168,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,19 +196,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -320,12 +335,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$26</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$26</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$26</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$26</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$29</f>
             </numRef>
           </val>
         </ser>
@@ -467,12 +482,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$26</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$26</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$29</f>
             </numRef>
           </val>
         </ser>
@@ -897,7 +912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 22/08/2026 (19j). Livree. lun-sam. Mise a jour 23/08/2026.</t>
+          <t>01/08 au 25/08/2026 (21j). Livree. lun-sam. Mise a jour 26/08/2026.</t>
         </is>
       </c>
     </row>
@@ -940,37 +955,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>650.3</v>
+        <v>759.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>34.2</v>
+        <v>36.2</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-39.3 t/j</t>
+          <t>-37.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>377.5</v>
+        <v>423.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-2.7 t/j</t>
+          <t>-11.5 t/j</t>
         </is>
       </c>
     </row>
@@ -986,37 +1001,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>376.9</v>
+        <v>421.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-38.1 t/j</t>
+          <t>-37.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>356.2</v>
+        <v>401.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-13.0 t/j</t>
+          <t>-3.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1032,14 +1047,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>198.4</v>
+        <v>230.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-5.8 t/j</t>
+          <t>-5.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1055,14 +1070,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>166.7</v>
+        <v>181.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-5.0 t/j</t>
+          <t>-5.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1078,14 +1093,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>160.4</v>
+        <v>181.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.8 t/j</t>
+          <t>-2.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1101,14 +1116,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>145.6</v>
+        <v>159.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.4 t/j</t>
+          <t>-4.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1139,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>142.3</v>
+        <v>151.3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.5 t/j</t>
+          <t>-3.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1162,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>117.8</v>
+        <v>129.6</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>6.2</v>
@@ -1161,46 +1176,46 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>107.3</v>
+        <v>118.5</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>105.2</v>
+        <v>107.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-3.6 t/j</t>
+          <t>-0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1231,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>93.2</v>
+        <v>107</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-0.9 t/j</t>
+          <t>-0.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1239,10 +1254,10 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
@@ -1285,10 +1300,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1205</v>
+        <v>1413.7</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>63.4</v>
+        <v>67.3</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1304,10 +1319,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>977.4</v>
+        <v>1073.6</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1323,10 +1338,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>889.8</v>
+        <v>969.9</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1338,14 +1353,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>3086.3</v>
+        <v>3471.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>162.4</v>
+        <v>165.3</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-117.8 t/j vs 280.2</t>
+          <t>-114.9 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1374,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 162.4 t/j (3248 sacs) sur 19j.</t>
+          <t>Moyenne/jour globale: 165.3 t/j (3305 sacs) sur 21j.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1396,7 +1411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 22/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 25/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1462,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -1471,76 +1486,76 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>0.8:1</t>
+          <t>2.0:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>+9 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>5.5:1</t>
+          <t>1.7:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>-11 cmdes</t>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1549,29 +1564,29 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>3.0:1</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>+8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1580,51 +1595,51 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>3.6:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
+          <t>1.4:1</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>-4 cmdes</t>
         </is>
@@ -1633,7 +1648,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1642,60 +1657,60 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>0.3:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>0.8:1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1704,156 +1719,140 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>3.2:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Ahala</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>-68 cmdes vs 119</t>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>-50 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
@@ -1865,37 +1864,22 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.0:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 1.2:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1912,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1929,7 +1913,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 22/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1993,29 +1977,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130859</t>
+          <t>SO2608-131418</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00618 -  FOTSO BRUNO</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2034,17 +2018,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130836</t>
+          <t>SO2608-131291</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00289 -  LIEDJI ALAIN PIERRE</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2053,10 +2037,10 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2075,29 +2059,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130822</t>
+          <t>SO2608-131351</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2116,7 +2100,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130887</t>
+          <t>SO2608-131352</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2135,10 +2119,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2157,29 +2141,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130788</t>
+          <t>SO2608-131314</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2198,17 +2182,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130841</t>
+          <t>SO2608-131409</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2217,10 +2201,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2239,17 +2223,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130819</t>
+          <t>SO2608-131339</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2258,10 +2242,10 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2280,29 +2264,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-130846</t>
+          <t>SO2608-131347</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2316,115 +2300,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130852</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>SO2608-130795</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 10 cmdes (4.7 t) le 22/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 8 cmdes (0.7 t) le 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2462,34 +2364,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 22/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 25/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>1. STOCK PHYSIQUE AU 01/08/2026 (magasins centraux BEKOKO)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Nb sacs</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Poids (t)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Équivalent sacs 50kg</t>
         </is>
@@ -2560,76 +2462,76 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>STOCK BRUT TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="15" t="n">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="16" t="n">
         <v>4021.5</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>80430</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Moins: allocation SPC (entité soeur)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>460</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>9200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>STOCK NET DISPONIBLE BELGOCAM</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="20" t="n">
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="21" t="n">
         <v>3561.5</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>71230</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>2. CONSOMMATION SOJA (vente directe + production concentrés)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Flux</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Sacs/sem (lun-sam)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Sacs/jour</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>t/sem</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2642,17 +2544,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18042</v>
+        <v>16566</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3007</v>
+        <v>2761</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>902</v>
+        <v>828</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 19j (Livrée)</t>
+          <t>Ventes août 21j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2720,90 +2622,90 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>TOTAL MIN</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
-        <v>22542</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>3757</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>1127</v>
-      </c>
-      <c r="E20" s="16" t="n"/>
+      <c r="B20" s="16" t="n">
+        <v>21066</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>3511</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>TOTAL MOY</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n">
-        <v>22942</v>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>3824</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>1147</v>
-      </c>
-      <c r="E21" s="16" t="n"/>
+      <c r="B21" s="16" t="n">
+        <v>21466</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>3578</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>1073</v>
+      </c>
+      <c r="E21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>TOTAL MAX</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n">
-        <v>23342</v>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>3890</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>1167</v>
-      </c>
-      <c r="E22" s="16" t="n"/>
+      <c r="B22" s="16" t="n">
+        <v>21866</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>3644</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>1093</v>
+      </c>
+      <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 22/08/2026)</t>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 25/08/2026)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Stock net (sacs éq. 50kg)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Conso (sacs/sem)</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Jours restants</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Semaines</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>Date rupture</t>
         </is>
@@ -2819,17 +2721,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>22542</v>
+        <v>21066</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>13/09/2026</t>
+        <v>3.4</v>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>
@@ -2843,17 +2745,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>22942</v>
+        <v>21466</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
+        <v>3.3</v>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>
@@ -2867,17 +2769,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23342</v>
+        <v>21866</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
+        <v>3.3</v>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
         </is>
       </c>
     </row>
@@ -2889,30 +2791,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 12/09/2026 (21 jours, 3.1 semaines).</t>
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 17/09/2026 (23 jours, 3.3 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 02/09/2026 (10 jours de marge).</t>
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 07/09/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Méthode: stock net = brut - 9 200 sacs SPC. Consommation = vente directe + production concentrés (4500-5300 sacs/sem).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 22/08/2026 (19j).</t>
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 25/08/2026 (21j).</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2949,7 +2851,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 22/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 25/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3020,26 +2922,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3147,18 +3049,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>141.9</v>
+        <v>162.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.31:1</t>
+          <t>2.38:1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="11">
@@ -3176,10 +3078,10 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>188.7</v>
+        <v>198.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>59.9</v>
+        <v>63.2</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -3220,26 +3122,26 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3289,18 +3191,18 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>207.4</v>
+        <v>211.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>84</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.47:1</t>
+          <t>2.45:1</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="16">
@@ -3347,18 +3249,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2.24:1</t>
+          <t>2.22:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="18">
@@ -3376,18 +3278,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>127.2</v>
+        <v>128.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>60.9</v>
+        <v>61.2</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2.09:1</t>
+          <t>2.1:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -3420,26 +3322,26 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>16/08/2026</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3460,18 +3362,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2.08:1</t>
+          <t>2.09:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="22">
@@ -3489,10 +3391,10 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>342.7</v>
+        <v>344.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>141.6</v>
+        <v>142.4</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -3547,10 +3449,10 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>137.7</v>
+        <v>144.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -3576,18 +3478,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>59.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>27.9</v>
+        <v>32.6</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2.15:1</t>
+          <t>2.22:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="26">
@@ -3605,57 +3507,141 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2.01:1</t>
+          <t>2.0:1</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>261.3</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2.35:1</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1.19:1</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 25-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 25-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 26-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 26-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -335,12 +335,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$29</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$29</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -370,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$29</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$29</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -482,12 +482,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$29</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$29</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 25/08/2026 (21j). Livree. lun-sam. Mise a jour 26/08/2026.</t>
+          <t>01/08 au 26/08/2026 (22j). Livree. lun-sam. Mise a jour 27/08/2026.</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>759.8</v>
+        <v>897.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>36.2</v>
+        <v>40.8</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-37.3 t/j</t>
+          <t>-17.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -978,37 +978,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>423.7</v>
+        <v>775.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.2</v>
+        <v>35.3</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-11.5 t/j</t>
+          <t>-38.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>421.7</v>
+        <v>429.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-37.9 t/j</t>
+          <t>-12.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>401.9</v>
+        <v>403.1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-3.4 t/j</t>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1047,14 +1047,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>230.2</v>
+        <v>238.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-5.3 t/j</t>
+          <t>-5.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1070,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>181.6</v>
+        <v>195.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-5.1 t/j</t>
+          <t>-4.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>181.3</v>
+        <v>189.5</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>8.6</v>
@@ -1116,14 +1116,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>159.7</v>
+        <v>172.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.5 t/j</t>
+          <t>-4.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1139,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>151.3</v>
+        <v>164.3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.8 t/j</t>
+          <t>-3.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1165,11 +1165,11 @@
         <v>129.6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1185,33 +1185,33 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>118.5</v>
+        <v>122.7</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-3.5 t/j</t>
+          <t>-3.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>107.7</v>
+        <v>109.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -1222,23 +1222,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>107</v>
+        <v>109.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-0.7 t/j</t>
+          <t>-1.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1254,14 +1254,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>83.2</v>
+        <v>84.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+1.1 t/j</t>
+          <t>+1.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1413.7</v>
+        <v>1443.8</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>67.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1073.6</v>
+        <v>1105.6</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>969.9</v>
+        <v>1473.6</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>46.2</v>
+        <v>67</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1353,14 +1353,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>3471.2</v>
+        <v>4037</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>165.3</v>
+        <v>183.5</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-114.9 t/j vs 280.2</t>
+          <t>-96.7 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 165.3 t/j (3305 sacs) sur 21j.</t>
+          <t>Moyenne/jour globale: 183.5 t/j (3669 sacs) sur 22j.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1411,7 +1411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 25/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 26/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1462,31 +1462,31 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>4.2:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>+9 cmdes</t>
+          <t>+12 cmdes</t>
         </is>
       </c>
     </row>
@@ -1533,91 +1533,91 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>+8 cmdes</t>
+          <t>1.3:1</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1626,17 +1626,17 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.4:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -1648,238 +1648,331 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>0.8:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1.6:1</t>
+          <t>1.3:1</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Buea</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Messassi</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>-15 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Djeleng</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>0.0:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-7 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>1.2:1</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>-50 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>1.4:1</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>-53 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>3-5:1</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>5-10:1</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>3-5:1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>5-10:1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 1.2:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 1.4:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1896,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1913,7 +2006,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 25/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1977,17 +2070,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131418</t>
+          <t>SO2608-131644</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2508-13553 -  KONGNE BRUNO UNIVERS DE L'ELEVAGE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1996,10 +2089,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2018,22 +2111,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131291</t>
+          <t>SO2608-131503</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -2059,7 +2152,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131351</t>
+          <t>SO2608-131525</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2100,7 +2193,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131352</t>
+          <t>SO2608-131573</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2141,29 +2234,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131314</t>
+          <t>SO2608-131597</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2182,17 +2275,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131409</t>
+          <t>SO2608-131598</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2201,10 +2294,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2223,12 +2316,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131339</t>
+          <t>SO2608-131599</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -2242,10 +2335,10 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2264,69 +2357,151 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131347</t>
+          <t>SO2608-131625</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2509-13996 -  SIMO KAMGA FELIX</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-131529</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Village</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-131583</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 8 cmdes (0.7 t) le 25/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 10 cmdes (1.8 t) le 26/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2364,7 +2539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 25/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 26/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2544,17 +2719,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>16566</v>
+        <v>15951</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2761</v>
+        <v>2658</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>828</v>
+        <v>798</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 21j (Livrée)</t>
+          <t>Ventes août 22j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2628,13 +2803,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>21066</v>
+        <v>20451</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3511</v>
+        <v>3408</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1053</v>
+        <v>1023</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2645,13 +2820,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>21466</v>
+        <v>20851</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3578</v>
+        <v>3475</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1073</v>
+        <v>1043</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2662,20 +2837,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>21866</v>
+        <v>21251</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>3644</v>
+        <v>3542</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1093</v>
+        <v>1063</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 25/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 26/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2721,17 +2896,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>21066</v>
+        <v>20451</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>24</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>
@@ -2745,17 +2920,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>21466</v>
+        <v>20851</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2944,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>21866</v>
+        <v>21251</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>23</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
@@ -2793,14 +2968,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 17/09/2026 (23 jours, 3.3 semaines).</t>
+          <t>Date de rupture probable: 18/09/2026 (23 jours, 3.4 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 07/09/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 08/09/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2989,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 25/08/2026 (21j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 26/08/2026 (22j).</t>
         </is>
       </c>
     </row>
@@ -2829,7 +3004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2851,7 +3026,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 25/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 26/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -2907,18 +3082,18 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>190.3</v>
+        <v>194.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.78:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +3166,10 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>184.6</v>
+        <v>189.6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>71.7</v>
+        <v>73.7</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -3020,18 +3195,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>196.9</v>
+        <v>201.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.78:1</t>
+          <t>2.79:1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="10">
@@ -3078,18 +3253,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>198.7</v>
+        <v>199.9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>63.2</v>
+        <v>63.7</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.15:1</t>
+          <t>3.14:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="12">
@@ -3278,18 +3453,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>128.2</v>
+        <v>133.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>61.2</v>
+        <v>63.2</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
+          <t>2.11:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="19">
@@ -3391,10 +3566,10 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>344.7</v>
+        <v>347.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>142.4</v>
+        <v>143.8</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -3420,10 +3595,10 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>138.9</v>
+        <v>140.9</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -3478,18 +3653,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2.22:1</t>
+          <t>2.21:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="26">
@@ -3562,18 +3737,18 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>261.3</v>
+        <v>283.1</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>111</v>
+        <v>118.9</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2.35:1</t>
+          <t>2.38:1</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="29">
@@ -3591,57 +3766,86 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>59.9</v>
+        <v>532.6</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>50.4</v>
+        <v>56.1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>1.19:1</t>
+          <t>9.5:1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1.37:1</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 26-08" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 26-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 28-08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 28-08" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Août" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +82,11 @@
     </font>
     <font>
       <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -198,19 +203,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -335,12 +340,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$30</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$30</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -370,12 +375,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$30</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$30</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$32</f>
             </numRef>
           </val>
         </ser>
@@ -482,12 +487,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$30</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$30</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -912,7 +917,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 26/08/2026 (22j). Livree. lun-sam. Mise a jour 27/08/2026.</t>
+          <t>01/08 au 28/08/2026 (24j). Livree. lun-sam. Mise a jour 29/08/2026.</t>
         </is>
       </c>
     </row>
@@ -955,14 +960,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>897.8</v>
+        <v>908.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>40.8</v>
+        <v>37.9</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-17.1 t/j</t>
+          <t>-20.1 t/j</t>
         </is>
       </c>
     </row>
@@ -978,14 +983,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>775.6</v>
+        <v>810</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>35.3</v>
+        <v>33.8</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-38.3 t/j</t>
+          <t>-39.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1001,14 +1006,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>429.2</v>
+        <v>448.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19.5</v>
+        <v>18.7</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-12.2 t/j</t>
+          <t>-13.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1029,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>403.1</v>
+        <v>428.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-4.2 t/j</t>
+          <t>-4.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1047,14 +1052,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>238.9</v>
+        <v>245.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-5.4 t/j</t>
+          <t>-6.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1075,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>195.8</v>
+        <v>204.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4.9 t/j</t>
+          <t>-5.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1098,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>189.5</v>
+        <v>200.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.6 t/j</t>
+          <t>-2.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1116,14 +1121,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>172.9</v>
+        <v>186.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.2 t/j</t>
+          <t>-4.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1144,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>164.3</v>
+        <v>172.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.5 t/j</t>
+          <t>-3.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1162,44 +1167,44 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>129.6</v>
+        <v>147.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.5 t/j</t>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>122.7</v>
+        <v>128.7</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-3.6 t/j</t>
+          <t>-0.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1208,33 +1213,33 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>109.7</v>
+        <v>127.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-0.8 t/j</t>
+          <t>-3.8 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>109.1</v>
+        <v>115</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -1254,14 +1259,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+1.0 t/j</t>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1277,10 +1282,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>14</v>
+        <v>16.4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -1300,10 +1305,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1443.8</v>
+        <v>1504.3</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>65.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1105.6</v>
+        <v>1166.1</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>50.3</v>
+        <v>48.6</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1338,10 +1343,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1473.6</v>
+        <v>1543.5</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>67</v>
+        <v>64.3</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1353,14 +1358,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>4037</v>
+        <v>4230.3</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>183.5</v>
+        <v>176.3</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-96.7 t/j vs 280.2</t>
+          <t>-104.0 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1379,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 183.5 t/j (3669 sacs) sur 22j.</t>
+          <t>Moyenne/jour globale: 176.3 t/j (3525 sacs) sur 24j.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1411,7 +1416,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 26/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 28/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1462,212 +1467,212 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>4.2:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>+15 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>+12 cmdes</t>
+          <t>1.3:1</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>1.4:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>+5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.3:1</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>-8 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>+8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.8:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>-4 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1679,7 +1684,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1688,22 +1693,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>8.3:1</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
@@ -1719,29 +1724,29 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1.3:1</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1750,22 +1755,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>0.6:1</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>-3 cmdes</t>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
@@ -1781,198 +1786,260 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
+          <t>0.7:1</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>-15 cmdes</t>
+          <t>-11 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Nkoabang</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>0.6:1</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Mbouda</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="C18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>0.0:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>0.9:1</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>-7 cmdes</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>1.4:1</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>-53 cmdes vs 119</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>+1 cmdes vs 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>3-5:1</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>9%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>92%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>5-10:1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 1.4:1 (vs 2.6:1 le 31/07).</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 1.6:1 (vs 2.6:1 le 31/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 04/08 (dernier jour complet, 62 cmdes soja Livrées). Comparaison vs 31/07 (bilan juillet complet).</t>
         </is>
@@ -1989,7 +2056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2006,7 +2073,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 26/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2137,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131644</t>
+          <t>SO2608-131867</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2508-13553 -  KONGNE BRUNO UNIVERS DE L'ELEVAGE</t>
+          <t>CU2605-14488 -  ZEUFACK BEATRICE AIMEE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2111,29 +2178,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131503</t>
+          <t>SO2608-131936</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00700 -  KENNE MANFOUO IDRICE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2152,29 +2219,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131525</t>
+          <t>SO2608-132022</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2406-00112 -  TILA SONWA AURELIEN</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2193,29 +2260,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131573</t>
+          <t>SO2608-132056</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00463 -  TCHINDA STEPHANE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2234,29 +2301,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131597</t>
+          <t>SO2608-132084</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00439 -  MOUAFO MATHIAS</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2275,29 +2342,29 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131598</t>
+          <t>SO2608-132042</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2316,17 +2383,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131599</t>
+          <t>SO2608-131995</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2357,29 +2424,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131625</t>
+          <t>SO2608-131949</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2509-13996 -  SIMO KAMGA FELIX</t>
+          <t>CU2509-13964 -  Wafo Pum Ephrem</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2398,22 +2465,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131529</t>
+          <t>SO2608-131944</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00905 -  TCHUENTE NARCISSE</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -2439,22 +2506,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131583</t>
+          <t>SO2608-131971</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2509-13962 -  Atchogna Fabo epse Nyapey Alida</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -2475,33 +2542,197 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-131982</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Ndobo</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-132000</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Pk11</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-132078</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Village</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SO2608-132059</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 10 cmdes (1.8 t) le 26/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 14 cmdes (5.6 t) le 28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Precedent (31/07): 14 cmdes (3.9 t)</t>
         </is>
@@ -2539,7 +2770,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 26/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 28/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2719,17 +2950,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>15951</v>
+        <v>14656</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2658</v>
+        <v>2443</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>798</v>
+        <v>733</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 22j (Livrée)</t>
+          <t>Ventes août 24j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -2803,13 +3034,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>20451</v>
+        <v>19156</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3408</v>
+        <v>3193</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1023</v>
+        <v>958</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -2820,13 +3051,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>20851</v>
+        <v>19556</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3475</v>
+        <v>3259</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1043</v>
+        <v>978</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -2837,20 +3068,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>21251</v>
+        <v>19956</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>3542</v>
+        <v>3326</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1063</v>
+        <v>998</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 26/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 28/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2896,17 +3127,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20451</v>
+        <v>19156</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
     </row>
@@ -2920,17 +3151,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>20851</v>
+        <v>19556</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
@@ -2944,17 +3175,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>21251</v>
+        <v>19956</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
@@ -2968,14 +3199,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 18/09/2026 (23 jours, 3.4 semaines).</t>
+          <t>Date de rupture probable: 22/09/2026 (25 jours, 3.6 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 08/09/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 12/09/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3220,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 26/08/2026 (22j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 28/08/2026 (24j).</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3026,7 +3257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 26/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 28/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3537,18 +3768,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>137</v>
+        <v>141.4</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2.09:1</t>
+          <t>2.12:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="22">
@@ -3566,10 +3797,10 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>347.7</v>
+        <v>349.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>143.8</v>
+        <v>144.3</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -3595,10 +3826,10 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>140.9</v>
+        <v>141.9</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -3624,18 +3855,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>144.7</v>
+        <v>155.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>73.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>1.98:1</t>
+          <t>2.02:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="25">
@@ -3653,18 +3884,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>73.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>33.1</v>
+        <v>34.3</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2.21:1</t>
+          <t>2.24:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="26">
@@ -3682,18 +3913,18 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
+          <t>2.02:1</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="27">
@@ -3737,18 +3968,18 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>283.1</v>
+        <v>309.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>118.9</v>
+        <v>129.2</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2.38:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="29">
@@ -3766,18 +3997,18 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>532.6</v>
+        <v>542.6</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>56.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>9.5:1</t>
+          <t>8.09:1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9.5</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="30">
@@ -3795,57 +4026,115 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>44.9</v>
+        <v>52.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>32.9</v>
+        <v>37.2</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1.37:1</t>
+          <t>1.4:1</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1.24:1</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1.61:1</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_aout.xlsx
+++ b/download/analyse_soja_aout.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,15 +77,10 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
@@ -203,19 +198,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -340,12 +335,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$32</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$D$5:$D$32</f>
+              <f>'T5 - Tendance Août'!$D$5:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -375,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$32</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$E$5:$E$32</f>
+              <f>'T5 - Tendance Août'!$E$5:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -487,12 +482,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Août'!$A$5:$A$32</f>
+              <f>'T5 - Tendance Août'!$A$5:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Août'!$G$5:$G$32</f>
+              <f>'T5 - Tendance Août'!$G$5:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -917,7 +912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/08 au 28/08/2026 (24j). Livree. lun-sam. Mise a jour 29/08/2026.</t>
+          <t>01/08 au 29/08/2026 (25j). Livree. lun-sam. Mise a jour 31/08/2026.</t>
         </is>
       </c>
     </row>
@@ -960,14 +955,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>908.4</v>
+        <v>918.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>37.9</v>
+        <v>36.7</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-20.1 t/j</t>
+          <t>-21.2 t/j</t>
         </is>
       </c>
     </row>
@@ -983,14 +978,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>810</v>
+        <v>823</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>33.8</v>
+        <v>32.9</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-39.8 t/j</t>
+          <t>-40.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1006,14 +1001,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>448.3</v>
+        <v>453.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>18.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-13.0 t/j</t>
+          <t>-13.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1029,14 +1024,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>428.9</v>
+        <v>430.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-4.7 t/j</t>
+          <t>-5.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1052,14 +1047,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>245.9</v>
+        <v>251.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-6.0 t/j</t>
+          <t>-6.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1075,14 +1070,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>204.5</v>
+        <v>209.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-5.2 t/j</t>
+          <t>-5.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1098,14 +1093,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>200.5</v>
+        <v>202.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-2.9 t/j</t>
+          <t>-3.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1121,14 +1116,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>186.4</v>
+        <v>188.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-4.3 t/j</t>
+          <t>-4.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1142,11 @@
         <v>172.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-3.8 t/j</t>
+          <t>-4.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1167,14 +1162,14 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>147.3</v>
+        <v>150.4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1190,14 +1185,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>128.7</v>
+        <v>129</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.6 t/j</t>
+          <t>-0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1213,14 +1208,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>127.7</v>
+        <v>128.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-3.8 t/j</t>
+          <t>-4.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1236,14 +1231,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>115</v>
+        <v>116.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-1.0 t/j</t>
+          <t>-1.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1254,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>+0.9 t/j</t>
+          <t>+0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1300,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1504.3</v>
+        <v>1528.3</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>62.7</v>
+        <v>61.1</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1324,10 +1319,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1166.1</v>
+        <v>1176.8</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1343,10 +1338,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1543.5</v>
+        <v>1559.1</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>64.3</v>
+        <v>62.4</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -1358,14 +1353,14 @@
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>4230.3</v>
+        <v>4280.5</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>176.3</v>
+        <v>171.2</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>-104.0 t/j vs 280.2</t>
+          <t>-109.0 t/j vs 280.2</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1374,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 176.3 t/j (3525 sacs) sur 24j.</t>
+          <t>Moyenne/jour globale: 171.2 t/j (3424 sacs) sur 25j.</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 28/08/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 29/08/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1462,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1476,175 +1471,175 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+15 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1.3:1</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1.4:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>+5 cmdes</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>+6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.2:1</t>
+          <t>1.9:1</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>+8 cmdes</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>-2 cmdes</t>
         </is>
@@ -1653,60 +1648,60 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
+          <t>1.9:1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-12 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>8.3:1</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
+          <t>1.1:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>-3 cmdes</t>
         </is>
@@ -1724,22 +1719,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
@@ -1755,29 +1750,29 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>0.6:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-8 cmdes</t>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>-11 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1786,29 +1781,29 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0.7:1</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>-11 cmdes</t>
+          <t>6.0:1</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1817,84 +1812,84 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>0.6:1</t>
+          <t>0.5:1</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>0.9:1</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>0.3:1</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
@@ -1906,22 +1901,22 @@
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>14</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>1.6:1</t>
+          <t>1.8:1</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>+1 cmdes vs 119</t>
+          <t>-56 cmdes vs 119</t>
         </is>
       </c>
     </row>
@@ -1956,11 +1951,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
@@ -1971,11 +1966,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>4%</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1981,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -2034,7 +2029,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Ratio global: 1.6:1 (vs 2.6:1 le 31/07).</t>
+          <t>Ratio global: 1.8:1 (vs 2.6:1 le 31/07).</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2068,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 28/08/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2132,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131867</t>
+          <t>SO2608-132094</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2605-14488 -  ZEUFACK BEATRICE AIMEE</t>
+          <t>CU2407-00700 -  KENNE MANFOUO IDRICE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -2178,12 +2173,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131936</t>
+          <t>SO2608-132099</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00700 -  KENNE MANFOUO IDRICE</t>
+          <t>CU2407-00689 -  KENFACK</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2219,12 +2214,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132022</t>
+          <t>SO2608-132219</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00112 -  TILA SONWA AURELIEN</t>
+          <t>CU2602-14371 -  MANFOUO MATHIEU</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2260,29 +2255,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132056</t>
+          <t>SO2608-132213</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00463 -  TCHINDA STEPHANE</t>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2301,29 +2296,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132084</t>
+          <t>SO2608-132177</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00439 -  MOUAFO MATHIAS</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2342,22 +2337,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132042</t>
+          <t>SO2608-132180</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -2383,22 +2378,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131995</t>
+          <t>SO2608-132112</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -2424,17 +2419,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131949</t>
+          <t>SO2608-132155</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2509-13964 -  Wafo Pum Ephrem</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2443,10 +2438,10 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2465,17 +2460,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131944</t>
+          <t>SO2608-132169</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00905 -  TCHUENTE NARCISSE</t>
+          <t>CU2508-13529 -  TONGOU epse MABOUT S. JEANNE SALI</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -2484,10 +2479,10 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -2506,22 +2501,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131971</t>
+          <t>SO2608-132101</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2509-13962 -  Atchogna Fabo epse Nyapey Alida</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -2547,22 +2542,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SO2608-131982</t>
+          <t>SO2608-132120</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -2588,22 +2583,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132000</t>
+          <t>SO2608-132175</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -2629,22 +2624,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132078</t>
+          <t>SO2608-132211</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -2670,7 +2665,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SO2608-132059</t>
+          <t>SO2608-132193</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2716,10 +2711,10 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="8" t="n"/>
@@ -2727,7 +2722,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Total soja-only: 14 cmdes (5.6 t) le 28/08/2026</t>
+          <t>Total soja-only: 14 cmdes (4.1 t) le 29/08/2026</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2765,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 28/08/2026.</t>
+          <t>Stock physique au 01/08/2026 (magasins BEKOKO). Exclusion 9 200 sacs SPC. Consommation = Vente + Production conc. Mise à jour 29/08/2026.</t>
         </is>
       </c>
     </row>
@@ -2950,17 +2945,17 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>14656</v>
+        <v>14069</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2443</v>
+        <v>2345</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>733</v>
+        <v>703</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ventes août 24j (Livrée)</t>
+          <t>Ventes août 25j (Livrée)</t>
         </is>
       </c>
     </row>
@@ -3034,13 +3029,13 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>19156</v>
+        <v>18569</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3193</v>
+        <v>3095</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>958</v>
+        <v>928</v>
       </c>
       <c r="E20" s="17" t="n"/>
     </row>
@@ -3051,13 +3046,13 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>19556</v>
+        <v>18969</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3259</v>
+        <v>3162</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>978</v>
+        <v>948</v>
       </c>
       <c r="E21" s="17" t="n"/>
     </row>
@@ -3068,20 +3063,20 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>19956</v>
+        <v>19369</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>3326</v>
+        <v>3228</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>998</v>
+        <v>968</v>
       </c>
       <c r="E22" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 28/08/2026)</t>
+          <t>3. DATE DE RUPTURE PROBABLE (stock net BELGOCAM, départ 29/08/2026)</t>
         </is>
       </c>
     </row>
@@ -3127,17 +3122,17 @@
         <v>71230</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>19156</v>
+        <v>18569</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
@@ -3151,17 +3146,17 @@
         <v>71230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>19556</v>
+        <v>18969</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
@@ -3175,17 +3170,17 @@
         <v>71230</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>19956</v>
+        <v>19369</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
     </row>
@@ -3199,14 +3194,14 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 22/09/2026 (25 jours, 3.6 semaines).</t>
+          <t>Date de rupture probable: 24/09/2026 (26 jours, 3.8 semaines).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>URGENCE: réapprovisionnement à prévoir avant le 12/09/2026 (10 jours de marge).</t>
+          <t>URGENCE: réapprovisionnement à prévoir avant le 14/09/2026 (10 jours de marge).</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3215,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 28/08/2026 (24j).</t>
+          <t>Le stock inclut tous les formats (50kg, 1kg, 5kg, 25kg) convertis en équivalent 50kg. Ventes août au 29/08/2026 (25j).</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3257,7 +3252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 28/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 29/08/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3884,18 +3879,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>76.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>34.3</v>
+        <v>35.4</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2.24:1</t>
+          <t>2.25:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="26">
@@ -3997,18 +3992,18 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>542.6</v>
+        <v>544.6</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>8.09:1</t>
+          <t>7.93:1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8.09</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="30">
@@ -4026,18 +4021,18 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1.4:1</t>
+          <t>1.41:1</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="31">
@@ -4055,18 +4050,18 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>1.24:1</t>
+          <t>1.26:1</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="32">
@@ -4084,57 +4079,86 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>53.9</v>
+        <v>61.1</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>1.61:1</t>
+          <t>1.54:1</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1.79:1</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début août) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>
